--- a/gratis/archivos/presupuestos-recibos/Presupuestos_y_Recibos_MixShopDigital.xlsx
+++ b/gratis/archivos/presupuestos-recibos/Presupuestos_y_Recibos_MixShopDigital.xlsx
@@ -48,7 +48,7 @@
     <numFmt numFmtId="168" formatCode="0;-0;&quot;-&quot;"/>
     <numFmt numFmtId="169" formatCode="0%;-0%;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -83,6 +83,12 @@
       <name val="Arial"/>
       <color rgb="00000000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000B2A7A"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -243,7 +249,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -270,6 +276,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF7A00"/>
+        <bgColor rgb="00FF7A00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFB800"/>
+        <bgColor rgb="00FFB800"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000094FB"/>
+        <bgColor rgb="000094FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFE9EE"/>
         <bgColor rgb="00FFE9EE"/>
       </patternFill>
@@ -282,14 +312,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FBF5F7"/>
-        <bgColor rgb="00FBF5F7"/>
+        <fgColor rgb="002ECC40"/>
+        <bgColor rgb="002ECC40"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="008727E2"/>
+        <bgColor rgb="008727E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBF5F7"/>
+        <bgColor rgb="00FBF5F7"/>
       </patternFill>
     </fill>
     <fill>
@@ -350,12 +386,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -364,274 +401,279 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="19" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="10" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="17" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="27" fillId="13" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="30" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="10" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="10" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="17" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="32" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="32" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="18" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="26" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="27" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="28" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="29" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="31" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="31" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1003,6 +1045,96 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>0</row>
+      <rowOff>76200</rowOff>
+    </from>
+    <ext cx="1409700" cy="285750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>0</row>
+      <rowOff>76200</rowOff>
+    </from>
+    <ext cx="1409700" cy="285750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>0</row>
+      <rowOff>76200</rowOff>
+    </from>
+    <ext cx="1409700" cy="285750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
       <col>7</col>
       <colOff>0</colOff>
       <row>13</row>
@@ -1043,6 +1175,91 @@
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>0</row>
+      <rowOff>76200</rowOff>
+    </from>
+    <ext cx="1409700" cy="285750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>0</row>
+      <rowOff>76200</rowOff>
+    </from>
+    <ext cx="1409700" cy="285750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>0</row>
+      <rowOff>76200</rowOff>
+    </from>
+    <ext cx="1409700" cy="285750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
     <clientData/>
   </oneCellAnchor>
 </wsDr>
@@ -1351,64 +1568,69 @@
     <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>MIX SHOP DIGITAL</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
+    <row r="1" ht="38" customHeight="1">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>PRESUPUESTO</t>
         </is>
       </c>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Armalo, imprimilo o guardalo en PDF</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="4" customHeight="1">
-      <c r="B3" s="5" t="n"/>
+    <row r="3" ht="5" customHeight="1">
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="9" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="11" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Completá las celdas amarillas. Los totales y el IVA se calculan solos. Para imprimir: Archivo &gt; Imprimir.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Recibo  →</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>Historial</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>Panel</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Ajustes</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Ayuda</t>
         </is>
@@ -1416,13 +1638,13 @@
     </row>
     <row r="7" ht="8" customHeight="1"/>
     <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="9">
+      <c r="B8" s="15">
         <f>UPPER(NombreNegocio)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="10">
+      <c r="B9" s="16">
         <f>IF(RucNegocio="","","RUC/C.I.: "&amp;RucNegocio&amp;"    ")&amp;IF(TelNegocio="","","Tel.: "&amp;TelNegocio&amp;"    ")&amp;DirNegocio</f>
         <v/>
       </c>
@@ -1438,73 +1660,73 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Presupuesto N°</t>
         </is>
       </c>
-      <c r="D11" s="12" t="n"/>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="D11" s="18" t="n"/>
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="G11" s="13" t="n"/>
+      <c r="G11" s="19" t="n"/>
       <c r="P11">
         <f>SUM(G18:G29)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="D12" s="14" t="n"/>
+      <c r="D12" s="20" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>RUC / C.I. del cliente</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n"/>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="D13" s="21" t="n"/>
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>Teléfono</t>
         </is>
       </c>
-      <c r="G13" s="16" t="n"/>
+      <c r="G13" s="22" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Válido hasta</t>
         </is>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="23">
         <f>IF(N(G11)=0,"",G11+Validez)</f>
         <v/>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>IVA</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t>10 %</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>Los precios que escribo…</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>Ya incluyen el IVA</t>
         </is>
@@ -1512,244 +1734,244 @@
     </row>
     <row r="16" ht="8" customHeight="1"/>
     <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Cant.</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Precio unitario</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>Desc. %</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="13" t="inlineStr">
         <is>
           <t>Importe</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="B18" s="18">
+      <c r="B18" s="24">
         <f>IF(C18&lt;&gt;"",1,"")</f>
         <v/>
       </c>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="19" t="n"/>
-      <c r="E18" s="20" t="n"/>
-      <c r="F18" s="21" t="n"/>
-      <c r="G18" s="22">
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="25" t="n"/>
+      <c r="E18" s="26" t="n"/>
+      <c r="F18" s="27" t="n"/>
+      <c r="G18" s="28">
         <f>IF(N(E18)=0,"",ROUND(IF(N(D18)&gt;0,D18,1)*E18*(1-N(F18)),Decimales))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="B19" s="23">
+      <c r="B19" s="29">
         <f>IF(C19&lt;&gt;"",2,"")</f>
         <v/>
       </c>
-      <c r="C19" s="14" t="n"/>
-      <c r="D19" s="19" t="n"/>
-      <c r="E19" s="20" t="n"/>
-      <c r="F19" s="21" t="n"/>
-      <c r="G19" s="24">
+      <c r="C19" s="20" t="n"/>
+      <c r="D19" s="25" t="n"/>
+      <c r="E19" s="26" t="n"/>
+      <c r="F19" s="27" t="n"/>
+      <c r="G19" s="30">
         <f>IF(N(E19)=0,"",ROUND(IF(N(D19)&gt;0,D19,1)*E19*(1-N(F19)),Decimales))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="B20" s="18">
+      <c r="B20" s="24">
         <f>IF(C20&lt;&gt;"",3,"")</f>
         <v/>
       </c>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="19" t="n"/>
-      <c r="E20" s="20" t="n"/>
-      <c r="F20" s="21" t="n"/>
-      <c r="G20" s="22">
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="25" t="n"/>
+      <c r="E20" s="26" t="n"/>
+      <c r="F20" s="27" t="n"/>
+      <c r="G20" s="28">
         <f>IF(N(E20)=0,"",ROUND(IF(N(D20)&gt;0,D20,1)*E20*(1-N(F20)),Decimales))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="B21" s="23">
+      <c r="B21" s="29">
         <f>IF(C21&lt;&gt;"",4,"")</f>
         <v/>
       </c>
-      <c r="C21" s="14" t="n"/>
-      <c r="D21" s="19" t="n"/>
-      <c r="E21" s="20" t="n"/>
-      <c r="F21" s="21" t="n"/>
-      <c r="G21" s="24">
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="25" t="n"/>
+      <c r="E21" s="26" t="n"/>
+      <c r="F21" s="27" t="n"/>
+      <c r="G21" s="30">
         <f>IF(N(E21)=0,"",ROUND(IF(N(D21)&gt;0,D21,1)*E21*(1-N(F21)),Decimales))</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="B22" s="18">
+      <c r="B22" s="24">
         <f>IF(C22&lt;&gt;"",5,"")</f>
         <v/>
       </c>
-      <c r="C22" s="14" t="n"/>
-      <c r="D22" s="19" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="21" t="n"/>
-      <c r="G22" s="22">
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="25" t="n"/>
+      <c r="E22" s="26" t="n"/>
+      <c r="F22" s="27" t="n"/>
+      <c r="G22" s="28">
         <f>IF(N(E22)=0,"",ROUND(IF(N(D22)&gt;0,D22,1)*E22*(1-N(F22)),Decimales))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="B23" s="23">
+      <c r="B23" s="29">
         <f>IF(C23&lt;&gt;"",6,"")</f>
         <v/>
       </c>
-      <c r="C23" s="14" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="20" t="n"/>
-      <c r="F23" s="21" t="n"/>
-      <c r="G23" s="24">
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="25" t="n"/>
+      <c r="E23" s="26" t="n"/>
+      <c r="F23" s="27" t="n"/>
+      <c r="G23" s="30">
         <f>IF(N(E23)=0,"",ROUND(IF(N(D23)&gt;0,D23,1)*E23*(1-N(F23)),Decimales))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="18">
+      <c r="B24" s="24">
         <f>IF(C24&lt;&gt;"",7,"")</f>
         <v/>
       </c>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="19" t="n"/>
-      <c r="E24" s="20" t="n"/>
-      <c r="F24" s="21" t="n"/>
-      <c r="G24" s="22">
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="25" t="n"/>
+      <c r="E24" s="26" t="n"/>
+      <c r="F24" s="27" t="n"/>
+      <c r="G24" s="28">
         <f>IF(N(E24)=0,"",ROUND(IF(N(D24)&gt;0,D24,1)*E24*(1-N(F24)),Decimales))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="B25" s="23">
+      <c r="B25" s="29">
         <f>IF(C25&lt;&gt;"",8,"")</f>
         <v/>
       </c>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="19" t="n"/>
-      <c r="E25" s="20" t="n"/>
-      <c r="F25" s="21" t="n"/>
-      <c r="G25" s="24">
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="25" t="n"/>
+      <c r="E25" s="26" t="n"/>
+      <c r="F25" s="27" t="n"/>
+      <c r="G25" s="30">
         <f>IF(N(E25)=0,"",ROUND(IF(N(D25)&gt;0,D25,1)*E25*(1-N(F25)),Decimales))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="B26" s="18">
+      <c r="B26" s="24">
         <f>IF(C26&lt;&gt;"",9,"")</f>
         <v/>
       </c>
-      <c r="C26" s="14" t="n"/>
-      <c r="D26" s="19" t="n"/>
-      <c r="E26" s="20" t="n"/>
-      <c r="F26" s="21" t="n"/>
-      <c r="G26" s="22">
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="25" t="n"/>
+      <c r="E26" s="26" t="n"/>
+      <c r="F26" s="27" t="n"/>
+      <c r="G26" s="28">
         <f>IF(N(E26)=0,"",ROUND(IF(N(D26)&gt;0,D26,1)*E26*(1-N(F26)),Decimales))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="B27" s="23">
+      <c r="B27" s="29">
         <f>IF(C27&lt;&gt;"",10,"")</f>
         <v/>
       </c>
-      <c r="C27" s="14" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="20" t="n"/>
-      <c r="F27" s="21" t="n"/>
-      <c r="G27" s="24">
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="25" t="n"/>
+      <c r="E27" s="26" t="n"/>
+      <c r="F27" s="27" t="n"/>
+      <c r="G27" s="30">
         <f>IF(N(E27)=0,"",ROUND(IF(N(D27)&gt;0,D27,1)*E27*(1-N(F27)),Decimales))</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="B28" s="18">
+      <c r="B28" s="24">
         <f>IF(C28&lt;&gt;"",11,"")</f>
         <v/>
       </c>
-      <c r="C28" s="14" t="n"/>
-      <c r="D28" s="19" t="n"/>
-      <c r="E28" s="20" t="n"/>
-      <c r="F28" s="21" t="n"/>
-      <c r="G28" s="22">
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="25" t="n"/>
+      <c r="E28" s="26" t="n"/>
+      <c r="F28" s="27" t="n"/>
+      <c r="G28" s="28">
         <f>IF(N(E28)=0,"",ROUND(IF(N(D28)&gt;0,D28,1)*E28*(1-N(F28)),Decimales))</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="B29" s="23">
+      <c r="B29" s="29">
         <f>IF(C29&lt;&gt;"",12,"")</f>
         <v/>
       </c>
-      <c r="C29" s="14" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="20" t="n"/>
-      <c r="F29" s="21" t="n"/>
-      <c r="G29" s="24">
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="25" t="n"/>
+      <c r="E29" s="26" t="n"/>
+      <c r="F29" s="27" t="n"/>
+      <c r="G29" s="30">
         <f>IF(N(E29)=0,"",ROUND(IF(N(D29)&gt;0,D29,1)*E29*(1-N(F29)),Decimales))</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="8" customHeight="1"/>
     <row r="31">
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B31" s="31" t="inlineStr">
         <is>
           <t>Condiciones y observaciones</t>
         </is>
       </c>
-      <c r="E31" s="26" t="inlineStr">
+      <c r="E31" s="32" t="inlineStr">
         <is>
           <t>Subtotal (sin IVA)</t>
         </is>
       </c>
-      <c r="G31" s="27">
+      <c r="G31" s="33">
         <f>IF(P10=1,P11-G32,P11)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="28" t="inlineStr">
+      <c r="B32" s="34" t="inlineStr">
         <is>
           <t>Forma de pago: a convenir.</t>
         </is>
       </c>
-      <c r="E32" s="26">
+      <c r="E32" s="32">
         <f>"IVA "&amp;IF(G14="Sin IVA","",G14)</f>
         <v/>
       </c>
-      <c r="G32" s="27">
+      <c r="G32" s="33">
         <f>IF(P9=0,0,IF(P10=1,ROUND(P11*P9/(1+P9),Decimales),ROUND(P11*P9,Decimales)))</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="E33" s="29">
+      <c r="E33" s="35">
         <f>"TOTAL "&amp;Moneda</f>
         <v/>
       </c>
-      <c r="F33" s="30" t="n"/>
-      <c r="G33" s="31">
+      <c r="F33" s="36" t="n"/>
+      <c r="G33" s="37">
         <f>G31+G32</f>
         <v/>
       </c>
@@ -1758,35 +1980,35 @@
     <row r="35"/>
     <row r="36" ht="30" customHeight="1"/>
     <row r="37">
-      <c r="B37" s="32" t="inlineStr">
+      <c r="B37" s="38" t="inlineStr">
         <is>
           <t>Firma del emisor</t>
         </is>
       </c>
-      <c r="E37" s="32" t="inlineStr">
+      <c r="E37" s="38" t="inlineStr">
         <is>
           <t>Conforme del cliente</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="33">
+      <c r="B39" s="39">
         <f>IF(N(G33)=0,"Escribí los ítems y el IVA y el total se calculan solos.","✔ Presupuesto listo. Anotalo en HISTORIAL para llevar el seguimiento.")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="8" customHeight="1">
-      <c r="B41" s="34" t="n"/>
+      <c r="B41" s="40" t="n"/>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="B42" s="35" t="inlineStr">
+      <c r="B42" s="41" t="inlineStr">
         <is>
           <t>MIX SHOP DIGITAL  ·  Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="B43" s="36" t="inlineStr">
+      <c r="B43" s="42" t="inlineStr">
         <is>
           <t>Versión gratuita  ·  Para gestionar todo tu negocio en un solo lugar, conocé Mi Negocio PY  →  mixshopdigital.com.py</t>
         </is>
@@ -1794,7 +2016,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8CA3"/>
-  <mergeCells count="34">
+  <mergeCells count="33">
     <mergeCell ref="B42:G42"/>
     <mergeCell ref="D12:G12"/>
     <mergeCell ref="E33:F33"/>
@@ -1819,7 +2041,6 @@
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B41:G41"/>
     <mergeCell ref="D2:G2"/>
-    <mergeCell ref="B3:G3"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B31:D31"/>
@@ -1871,6 +2092,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1894,238 +2116,243 @@
     <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>MIX SHOP DIGITAL</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
+    <row r="1" ht="38" customHeight="1">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>RECIBO</t>
         </is>
       </c>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Constancia de pago</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="4" customHeight="1">
-      <c r="B3" s="5" t="n"/>
+    <row r="3" ht="5" customHeight="1">
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="9" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="11" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="B4" s="37" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="B4" s="43" t="n"/>
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Completá lo que quieras: si dejás celdas vacías, se toman los datos del presupuesto.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>←  Presupuesto</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>Historial</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>Panel</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="38" t="inlineStr">
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>1. COMPLETÁ (todo es opcional salvo el N°)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Recibo N°</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n"/>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="D8" s="18" t="n"/>
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="G8" s="13" t="n"/>
+      <c r="G8" s="19" t="n"/>
       <c r="P8">
         <f>IF(N(D10)&gt;0,D10,N(PRESUPUESTO!G33))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Recibí de</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n"/>
+      <c r="D9" s="20" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Monto recibido</t>
         </is>
       </c>
-      <c r="D10" s="39" t="n"/>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="D10" s="45" t="n"/>
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>Pago</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>Efectivo</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="D11" s="14" t="n"/>
+      <c r="D11" s="20" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="40" t="inlineStr">
+      <c r="B12" s="46" t="inlineStr">
         <is>
           <t>Vacío = se usan el cliente, el total y el N° del presupuesto.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="41" t="inlineStr">
+      <c r="B14" s="47" t="inlineStr">
         <is>
           <t>2. RECIBO (lo que se imprime)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="B15" s="42">
+      <c r="B15" s="48">
         <f>UPPER(NombreNegocio)&amp;IF(RucNegocio="",""," · RUC "&amp;RucNegocio)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="B16" s="43">
+      <c r="B16" s="49">
         <f>"RECIBO N° "&amp;IF(D8="","____",D8)</f>
         <v/>
       </c>
-      <c r="E16" s="44">
+      <c r="E16" s="50">
         <f>IF(N(G8)=0,"Fecha: ____","Fecha: "&amp;RIGHT("0"&amp;DAY(G8),2)&amp;"/"&amp;RIGHT("0"&amp;MONTH(G8),2)&amp;"/"&amp;YEAR(G8))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="45" t="inlineStr">
+      <c r="B17" s="51" t="inlineStr">
         <is>
           <t>Recibí de</t>
         </is>
       </c>
-      <c r="D17" s="46">
+      <c r="D17" s="52">
         <f>IF(D9&lt;&gt;"",D9,IF(PRESUPUESTO!D12&lt;&gt;"",PRESUPUESTO!D12,"____________________"))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="B18" s="45" t="inlineStr">
+      <c r="B18" s="51" t="inlineStr">
         <is>
           <t>La suma de</t>
         </is>
       </c>
-      <c r="D18" s="47">
+      <c r="D18" s="53">
         <f>FIXED(P8,Decimales)&amp;" "&amp;Moneda</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="B19" s="45" t="inlineStr">
+      <c r="B19" s="51" t="inlineStr">
         <is>
           <t>Por concepto de</t>
         </is>
       </c>
-      <c r="D19" s="46">
+      <c r="D19" s="52">
         <f>IF(D11&lt;&gt;"",D11,IF(PRESUPUESTO!D11&lt;&gt;"","Pago del presupuesto N° "&amp;PRESUPUESTO!D11,"Pago a cuenta"))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="45" t="inlineStr">
+      <c r="B20" s="51" t="inlineStr">
         <is>
           <t>Forma de pago</t>
         </is>
       </c>
-      <c r="D20" s="46">
+      <c r="D20" s="52">
         <f>IF(G10="","Efectivo",G10)</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="45" t="inlineStr">
+      <c r="B21" s="51" t="inlineStr">
         <is>
           <t>Total del presupuesto</t>
         </is>
       </c>
-      <c r="D21" s="46">
+      <c r="D21" s="52">
         <f>IF(N(PRESUPUESTO!G33)=0,"-",FIXED(PRESUPUESTO!G33,Decimales)&amp;" "&amp;Moneda)</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="45" t="inlineStr">
+      <c r="B22" s="51" t="inlineStr">
         <is>
           <t>Saldo pendiente</t>
         </is>
       </c>
-      <c r="D22" s="46">
+      <c r="D22" s="52">
         <f>IF(N(PRESUPUESTO!G33)=0,"-",IF(PRESUPUESTO!G33-P8&lt;=0,"Pago total — sin saldo",FIXED(PRESUPUESTO!G33-P8,Decimales)&amp;" "&amp;Moneda&amp;"  (pago parcial)"))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1"/>
     <row r="24" ht="18" customHeight="1">
-      <c r="B24" s="32" t="inlineStr">
+      <c r="B24" s="38" t="inlineStr">
         <is>
           <t>Firma y aclaración</t>
         </is>
       </c>
-      <c r="E24" s="32" t="inlineStr">
+      <c r="E24" s="38" t="inlineStr">
         <is>
           <t>Recibí conforme</t>
         </is>
       </c>
     </row>
     <row r="27" ht="8" customHeight="1">
-      <c r="B27" s="34" t="n"/>
+      <c r="B27" s="40" t="n"/>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="B28" s="35" t="inlineStr">
+      <c r="B28" s="41" t="inlineStr">
         <is>
           <t>MIX SHOP DIGITAL  ·  Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="B29" s="36" t="inlineStr">
+      <c r="B29" s="42" t="inlineStr">
         <is>
           <t>Versión gratuita  ·  Para gestionar todo tu negocio en un solo lugar, conocé Mi Negocio PY  →  mixshopdigital.com.py</t>
         </is>
@@ -2133,7 +2360,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8CA3"/>
-  <mergeCells count="40">
+  <mergeCells count="39">
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="D9:G9"/>
     <mergeCell ref="D10:E10"/>
@@ -2164,7 +2391,6 @@
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="B7:G7"/>
     <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B3:G3"/>
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="E24:G24"/>
     <mergeCell ref="B24:C24"/>
@@ -2204,6 +2430,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2226,903 +2453,908 @@
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>MIX SHOP DIGITAL</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
+    <row r="1" ht="38" customHeight="1">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>HISTORIAL</t>
         </is>
       </c>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Seguimiento de tus presupuestos</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="4" customHeight="1">
-      <c r="B3" s="5" t="n"/>
+    <row r="3" ht="5" customHeight="1">
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="9" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="11" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="B4" s="37" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="B4" s="43" t="n"/>
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Una fila por presupuesto enviado. Cambiá el Estado cuando se apruebe o se cobre. Podés filtrar con la fila de títulos.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>←  Presupuesto</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>Ver panel  →</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="B6" s="48">
+      <c r="B6" s="54">
         <f>"Registros: "&amp;COUNT(F8:F107)&amp;" de 100   ·   Por cobrar: "&amp;FIXED(PANEL!E17,Decimales)&amp;" "&amp;Moneda</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Detalle (opcional)</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>Monto total</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="49" t="n"/>
-      <c r="D8" s="50" t="n"/>
-      <c r="E8" s="50" t="n"/>
-      <c r="F8" s="51" t="n"/>
-      <c r="G8" s="16" t="n"/>
+      <c r="B8" s="22" t="n"/>
+      <c r="C8" s="55" t="n"/>
+      <c r="D8" s="56" t="n"/>
+      <c r="E8" s="56" t="n"/>
+      <c r="F8" s="57" t="n"/>
+      <c r="G8" s="22" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="49" t="n"/>
-      <c r="D9" s="50" t="n"/>
-      <c r="E9" s="50" t="n"/>
-      <c r="F9" s="51" t="n"/>
-      <c r="G9" s="16" t="n"/>
+      <c r="B9" s="22" t="n"/>
+      <c r="C9" s="55" t="n"/>
+      <c r="D9" s="56" t="n"/>
+      <c r="E9" s="56" t="n"/>
+      <c r="F9" s="57" t="n"/>
+      <c r="G9" s="22" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="49" t="n"/>
-      <c r="D10" s="50" t="n"/>
-      <c r="E10" s="50" t="n"/>
-      <c r="F10" s="51" t="n"/>
-      <c r="G10" s="16" t="n"/>
+      <c r="B10" s="22" t="n"/>
+      <c r="C10" s="55" t="n"/>
+      <c r="D10" s="56" t="n"/>
+      <c r="E10" s="56" t="n"/>
+      <c r="F10" s="57" t="n"/>
+      <c r="G10" s="22" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="49" t="n"/>
-      <c r="D11" s="50" t="n"/>
-      <c r="E11" s="50" t="n"/>
-      <c r="F11" s="51" t="n"/>
-      <c r="G11" s="16" t="n"/>
+      <c r="B11" s="22" t="n"/>
+      <c r="C11" s="55" t="n"/>
+      <c r="D11" s="56" t="n"/>
+      <c r="E11" s="56" t="n"/>
+      <c r="F11" s="57" t="n"/>
+      <c r="G11" s="22" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="49" t="n"/>
-      <c r="D12" s="50" t="n"/>
-      <c r="E12" s="50" t="n"/>
-      <c r="F12" s="51" t="n"/>
-      <c r="G12" s="16" t="n"/>
+      <c r="B12" s="22" t="n"/>
+      <c r="C12" s="55" t="n"/>
+      <c r="D12" s="56" t="n"/>
+      <c r="E12" s="56" t="n"/>
+      <c r="F12" s="57" t="n"/>
+      <c r="G12" s="22" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="49" t="n"/>
-      <c r="D13" s="50" t="n"/>
-      <c r="E13" s="50" t="n"/>
-      <c r="F13" s="51" t="n"/>
-      <c r="G13" s="16" t="n"/>
+      <c r="B13" s="22" t="n"/>
+      <c r="C13" s="55" t="n"/>
+      <c r="D13" s="56" t="n"/>
+      <c r="E13" s="56" t="n"/>
+      <c r="F13" s="57" t="n"/>
+      <c r="G13" s="22" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="49" t="n"/>
-      <c r="D14" s="50" t="n"/>
-      <c r="E14" s="50" t="n"/>
-      <c r="F14" s="51" t="n"/>
-      <c r="G14" s="16" t="n"/>
+      <c r="B14" s="22" t="n"/>
+      <c r="C14" s="55" t="n"/>
+      <c r="D14" s="56" t="n"/>
+      <c r="E14" s="56" t="n"/>
+      <c r="F14" s="57" t="n"/>
+      <c r="G14" s="22" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="49" t="n"/>
-      <c r="D15" s="50" t="n"/>
-      <c r="E15" s="50" t="n"/>
-      <c r="F15" s="51" t="n"/>
-      <c r="G15" s="16" t="n"/>
+      <c r="B15" s="22" t="n"/>
+      <c r="C15" s="55" t="n"/>
+      <c r="D15" s="56" t="n"/>
+      <c r="E15" s="56" t="n"/>
+      <c r="F15" s="57" t="n"/>
+      <c r="G15" s="22" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="49" t="n"/>
-      <c r="D16" s="50" t="n"/>
-      <c r="E16" s="50" t="n"/>
-      <c r="F16" s="51" t="n"/>
-      <c r="G16" s="16" t="n"/>
+      <c r="B16" s="22" t="n"/>
+      <c r="C16" s="55" t="n"/>
+      <c r="D16" s="56" t="n"/>
+      <c r="E16" s="56" t="n"/>
+      <c r="F16" s="57" t="n"/>
+      <c r="G16" s="22" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="49" t="n"/>
-      <c r="D17" s="50" t="n"/>
-      <c r="E17" s="50" t="n"/>
-      <c r="F17" s="51" t="n"/>
-      <c r="G17" s="16" t="n"/>
+      <c r="B17" s="22" t="n"/>
+      <c r="C17" s="55" t="n"/>
+      <c r="D17" s="56" t="n"/>
+      <c r="E17" s="56" t="n"/>
+      <c r="F17" s="57" t="n"/>
+      <c r="G17" s="22" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="49" t="n"/>
-      <c r="D18" s="50" t="n"/>
-      <c r="E18" s="50" t="n"/>
-      <c r="F18" s="51" t="n"/>
-      <c r="G18" s="16" t="n"/>
+      <c r="B18" s="22" t="n"/>
+      <c r="C18" s="55" t="n"/>
+      <c r="D18" s="56" t="n"/>
+      <c r="E18" s="56" t="n"/>
+      <c r="F18" s="57" t="n"/>
+      <c r="G18" s="22" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="49" t="n"/>
-      <c r="D19" s="50" t="n"/>
-      <c r="E19" s="50" t="n"/>
-      <c r="F19" s="51" t="n"/>
-      <c r="G19" s="16" t="n"/>
+      <c r="B19" s="22" t="n"/>
+      <c r="C19" s="55" t="n"/>
+      <c r="D19" s="56" t="n"/>
+      <c r="E19" s="56" t="n"/>
+      <c r="F19" s="57" t="n"/>
+      <c r="G19" s="22" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="49" t="n"/>
-      <c r="D20" s="50" t="n"/>
-      <c r="E20" s="50" t="n"/>
-      <c r="F20" s="51" t="n"/>
-      <c r="G20" s="16" t="n"/>
+      <c r="B20" s="22" t="n"/>
+      <c r="C20" s="55" t="n"/>
+      <c r="D20" s="56" t="n"/>
+      <c r="E20" s="56" t="n"/>
+      <c r="F20" s="57" t="n"/>
+      <c r="G20" s="22" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="49" t="n"/>
-      <c r="D21" s="50" t="n"/>
-      <c r="E21" s="50" t="n"/>
-      <c r="F21" s="51" t="n"/>
-      <c r="G21" s="16" t="n"/>
+      <c r="B21" s="22" t="n"/>
+      <c r="C21" s="55" t="n"/>
+      <c r="D21" s="56" t="n"/>
+      <c r="E21" s="56" t="n"/>
+      <c r="F21" s="57" t="n"/>
+      <c r="G21" s="22" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="49" t="n"/>
-      <c r="D22" s="50" t="n"/>
-      <c r="E22" s="50" t="n"/>
-      <c r="F22" s="51" t="n"/>
-      <c r="G22" s="16" t="n"/>
+      <c r="B22" s="22" t="n"/>
+      <c r="C22" s="55" t="n"/>
+      <c r="D22" s="56" t="n"/>
+      <c r="E22" s="56" t="n"/>
+      <c r="F22" s="57" t="n"/>
+      <c r="G22" s="22" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="49" t="n"/>
-      <c r="D23" s="50" t="n"/>
-      <c r="E23" s="50" t="n"/>
-      <c r="F23" s="51" t="n"/>
-      <c r="G23" s="16" t="n"/>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="55" t="n"/>
+      <c r="D23" s="56" t="n"/>
+      <c r="E23" s="56" t="n"/>
+      <c r="F23" s="57" t="n"/>
+      <c r="G23" s="22" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="49" t="n"/>
-      <c r="D24" s="50" t="n"/>
-      <c r="E24" s="50" t="n"/>
-      <c r="F24" s="51" t="n"/>
-      <c r="G24" s="16" t="n"/>
+      <c r="B24" s="22" t="n"/>
+      <c r="C24" s="55" t="n"/>
+      <c r="D24" s="56" t="n"/>
+      <c r="E24" s="56" t="n"/>
+      <c r="F24" s="57" t="n"/>
+      <c r="G24" s="22" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="49" t="n"/>
-      <c r="D25" s="50" t="n"/>
-      <c r="E25" s="50" t="n"/>
-      <c r="F25" s="51" t="n"/>
-      <c r="G25" s="16" t="n"/>
+      <c r="B25" s="22" t="n"/>
+      <c r="C25" s="55" t="n"/>
+      <c r="D25" s="56" t="n"/>
+      <c r="E25" s="56" t="n"/>
+      <c r="F25" s="57" t="n"/>
+      <c r="G25" s="22" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="49" t="n"/>
-      <c r="D26" s="50" t="n"/>
-      <c r="E26" s="50" t="n"/>
-      <c r="F26" s="51" t="n"/>
-      <c r="G26" s="16" t="n"/>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="55" t="n"/>
+      <c r="D26" s="56" t="n"/>
+      <c r="E26" s="56" t="n"/>
+      <c r="F26" s="57" t="n"/>
+      <c r="G26" s="22" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="49" t="n"/>
-      <c r="D27" s="50" t="n"/>
-      <c r="E27" s="50" t="n"/>
-      <c r="F27" s="51" t="n"/>
-      <c r="G27" s="16" t="n"/>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="55" t="n"/>
+      <c r="D27" s="56" t="n"/>
+      <c r="E27" s="56" t="n"/>
+      <c r="F27" s="57" t="n"/>
+      <c r="G27" s="22" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="49" t="n"/>
-      <c r="D28" s="50" t="n"/>
-      <c r="E28" s="50" t="n"/>
-      <c r="F28" s="51" t="n"/>
-      <c r="G28" s="16" t="n"/>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="55" t="n"/>
+      <c r="D28" s="56" t="n"/>
+      <c r="E28" s="56" t="n"/>
+      <c r="F28" s="57" t="n"/>
+      <c r="G28" s="22" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="49" t="n"/>
-      <c r="D29" s="50" t="n"/>
-      <c r="E29" s="50" t="n"/>
-      <c r="F29" s="51" t="n"/>
-      <c r="G29" s="16" t="n"/>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="55" t="n"/>
+      <c r="D29" s="56" t="n"/>
+      <c r="E29" s="56" t="n"/>
+      <c r="F29" s="57" t="n"/>
+      <c r="G29" s="22" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="49" t="n"/>
-      <c r="D30" s="50" t="n"/>
-      <c r="E30" s="50" t="n"/>
-      <c r="F30" s="51" t="n"/>
-      <c r="G30" s="16" t="n"/>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="55" t="n"/>
+      <c r="D30" s="56" t="n"/>
+      <c r="E30" s="56" t="n"/>
+      <c r="F30" s="57" t="n"/>
+      <c r="G30" s="22" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="49" t="n"/>
-      <c r="D31" s="50" t="n"/>
-      <c r="E31" s="50" t="n"/>
-      <c r="F31" s="51" t="n"/>
-      <c r="G31" s="16" t="n"/>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="55" t="n"/>
+      <c r="D31" s="56" t="n"/>
+      <c r="E31" s="56" t="n"/>
+      <c r="F31" s="57" t="n"/>
+      <c r="G31" s="22" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="49" t="n"/>
-      <c r="D32" s="50" t="n"/>
-      <c r="E32" s="50" t="n"/>
-      <c r="F32" s="51" t="n"/>
-      <c r="G32" s="16" t="n"/>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="55" t="n"/>
+      <c r="D32" s="56" t="n"/>
+      <c r="E32" s="56" t="n"/>
+      <c r="F32" s="57" t="n"/>
+      <c r="G32" s="22" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="49" t="n"/>
-      <c r="D33" s="50" t="n"/>
-      <c r="E33" s="50" t="n"/>
-      <c r="F33" s="51" t="n"/>
-      <c r="G33" s="16" t="n"/>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="55" t="n"/>
+      <c r="D33" s="56" t="n"/>
+      <c r="E33" s="56" t="n"/>
+      <c r="F33" s="57" t="n"/>
+      <c r="G33" s="22" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="49" t="n"/>
-      <c r="D34" s="50" t="n"/>
-      <c r="E34" s="50" t="n"/>
-      <c r="F34" s="51" t="n"/>
-      <c r="G34" s="16" t="n"/>
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="55" t="n"/>
+      <c r="D34" s="56" t="n"/>
+      <c r="E34" s="56" t="n"/>
+      <c r="F34" s="57" t="n"/>
+      <c r="G34" s="22" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="49" t="n"/>
-      <c r="D35" s="50" t="n"/>
-      <c r="E35" s="50" t="n"/>
-      <c r="F35" s="51" t="n"/>
-      <c r="G35" s="16" t="n"/>
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="55" t="n"/>
+      <c r="D35" s="56" t="n"/>
+      <c r="E35" s="56" t="n"/>
+      <c r="F35" s="57" t="n"/>
+      <c r="G35" s="22" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="49" t="n"/>
-      <c r="D36" s="50" t="n"/>
-      <c r="E36" s="50" t="n"/>
-      <c r="F36" s="51" t="n"/>
-      <c r="G36" s="16" t="n"/>
+      <c r="B36" s="22" t="n"/>
+      <c r="C36" s="55" t="n"/>
+      <c r="D36" s="56" t="n"/>
+      <c r="E36" s="56" t="n"/>
+      <c r="F36" s="57" t="n"/>
+      <c r="G36" s="22" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="16" t="n"/>
-      <c r="C37" s="49" t="n"/>
-      <c r="D37" s="50" t="n"/>
-      <c r="E37" s="50" t="n"/>
-      <c r="F37" s="51" t="n"/>
-      <c r="G37" s="16" t="n"/>
+      <c r="B37" s="22" t="n"/>
+      <c r="C37" s="55" t="n"/>
+      <c r="D37" s="56" t="n"/>
+      <c r="E37" s="56" t="n"/>
+      <c r="F37" s="57" t="n"/>
+      <c r="G37" s="22" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="49" t="n"/>
-      <c r="D38" s="50" t="n"/>
-      <c r="E38" s="50" t="n"/>
-      <c r="F38" s="51" t="n"/>
-      <c r="G38" s="16" t="n"/>
+      <c r="B38" s="22" t="n"/>
+      <c r="C38" s="55" t="n"/>
+      <c r="D38" s="56" t="n"/>
+      <c r="E38" s="56" t="n"/>
+      <c r="F38" s="57" t="n"/>
+      <c r="G38" s="22" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="49" t="n"/>
-      <c r="D39" s="50" t="n"/>
-      <c r="E39" s="50" t="n"/>
-      <c r="F39" s="51" t="n"/>
-      <c r="G39" s="16" t="n"/>
+      <c r="B39" s="22" t="n"/>
+      <c r="C39" s="55" t="n"/>
+      <c r="D39" s="56" t="n"/>
+      <c r="E39" s="56" t="n"/>
+      <c r="F39" s="57" t="n"/>
+      <c r="G39" s="22" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="49" t="n"/>
-      <c r="D40" s="50" t="n"/>
-      <c r="E40" s="50" t="n"/>
-      <c r="F40" s="51" t="n"/>
-      <c r="G40" s="16" t="n"/>
+      <c r="B40" s="22" t="n"/>
+      <c r="C40" s="55" t="n"/>
+      <c r="D40" s="56" t="n"/>
+      <c r="E40" s="56" t="n"/>
+      <c r="F40" s="57" t="n"/>
+      <c r="G40" s="22" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="49" t="n"/>
-      <c r="D41" s="50" t="n"/>
-      <c r="E41" s="50" t="n"/>
-      <c r="F41" s="51" t="n"/>
-      <c r="G41" s="16" t="n"/>
+      <c r="B41" s="22" t="n"/>
+      <c r="C41" s="55" t="n"/>
+      <c r="D41" s="56" t="n"/>
+      <c r="E41" s="56" t="n"/>
+      <c r="F41" s="57" t="n"/>
+      <c r="G41" s="22" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="49" t="n"/>
-      <c r="D42" s="50" t="n"/>
-      <c r="E42" s="50" t="n"/>
-      <c r="F42" s="51" t="n"/>
-      <c r="G42" s="16" t="n"/>
+      <c r="B42" s="22" t="n"/>
+      <c r="C42" s="55" t="n"/>
+      <c r="D42" s="56" t="n"/>
+      <c r="E42" s="56" t="n"/>
+      <c r="F42" s="57" t="n"/>
+      <c r="G42" s="22" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="49" t="n"/>
-      <c r="D43" s="50" t="n"/>
-      <c r="E43" s="50" t="n"/>
-      <c r="F43" s="51" t="n"/>
-      <c r="G43" s="16" t="n"/>
+      <c r="B43" s="22" t="n"/>
+      <c r="C43" s="55" t="n"/>
+      <c r="D43" s="56" t="n"/>
+      <c r="E43" s="56" t="n"/>
+      <c r="F43" s="57" t="n"/>
+      <c r="G43" s="22" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="49" t="n"/>
-      <c r="D44" s="50" t="n"/>
-      <c r="E44" s="50" t="n"/>
-      <c r="F44" s="51" t="n"/>
-      <c r="G44" s="16" t="n"/>
+      <c r="B44" s="22" t="n"/>
+      <c r="C44" s="55" t="n"/>
+      <c r="D44" s="56" t="n"/>
+      <c r="E44" s="56" t="n"/>
+      <c r="F44" s="57" t="n"/>
+      <c r="G44" s="22" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="49" t="n"/>
-      <c r="D45" s="50" t="n"/>
-      <c r="E45" s="50" t="n"/>
-      <c r="F45" s="51" t="n"/>
-      <c r="G45" s="16" t="n"/>
+      <c r="B45" s="22" t="n"/>
+      <c r="C45" s="55" t="n"/>
+      <c r="D45" s="56" t="n"/>
+      <c r="E45" s="56" t="n"/>
+      <c r="F45" s="57" t="n"/>
+      <c r="G45" s="22" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="49" t="n"/>
-      <c r="D46" s="50" t="n"/>
-      <c r="E46" s="50" t="n"/>
-      <c r="F46" s="51" t="n"/>
-      <c r="G46" s="16" t="n"/>
+      <c r="B46" s="22" t="n"/>
+      <c r="C46" s="55" t="n"/>
+      <c r="D46" s="56" t="n"/>
+      <c r="E46" s="56" t="n"/>
+      <c r="F46" s="57" t="n"/>
+      <c r="G46" s="22" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="49" t="n"/>
-      <c r="D47" s="50" t="n"/>
-      <c r="E47" s="50" t="n"/>
-      <c r="F47" s="51" t="n"/>
-      <c r="G47" s="16" t="n"/>
+      <c r="B47" s="22" t="n"/>
+      <c r="C47" s="55" t="n"/>
+      <c r="D47" s="56" t="n"/>
+      <c r="E47" s="56" t="n"/>
+      <c r="F47" s="57" t="n"/>
+      <c r="G47" s="22" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="49" t="n"/>
-      <c r="D48" s="50" t="n"/>
-      <c r="E48" s="50" t="n"/>
-      <c r="F48" s="51" t="n"/>
-      <c r="G48" s="16" t="n"/>
+      <c r="B48" s="22" t="n"/>
+      <c r="C48" s="55" t="n"/>
+      <c r="D48" s="56" t="n"/>
+      <c r="E48" s="56" t="n"/>
+      <c r="F48" s="57" t="n"/>
+      <c r="G48" s="22" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="49" t="n"/>
-      <c r="D49" s="50" t="n"/>
-      <c r="E49" s="50" t="n"/>
-      <c r="F49" s="51" t="n"/>
-      <c r="G49" s="16" t="n"/>
+      <c r="B49" s="22" t="n"/>
+      <c r="C49" s="55" t="n"/>
+      <c r="D49" s="56" t="n"/>
+      <c r="E49" s="56" t="n"/>
+      <c r="F49" s="57" t="n"/>
+      <c r="G49" s="22" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="16" t="n"/>
-      <c r="C50" s="49" t="n"/>
-      <c r="D50" s="50" t="n"/>
-      <c r="E50" s="50" t="n"/>
-      <c r="F50" s="51" t="n"/>
-      <c r="G50" s="16" t="n"/>
+      <c r="B50" s="22" t="n"/>
+      <c r="C50" s="55" t="n"/>
+      <c r="D50" s="56" t="n"/>
+      <c r="E50" s="56" t="n"/>
+      <c r="F50" s="57" t="n"/>
+      <c r="G50" s="22" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="16" t="n"/>
-      <c r="C51" s="49" t="n"/>
-      <c r="D51" s="50" t="n"/>
-      <c r="E51" s="50" t="n"/>
-      <c r="F51" s="51" t="n"/>
-      <c r="G51" s="16" t="n"/>
+      <c r="B51" s="22" t="n"/>
+      <c r="C51" s="55" t="n"/>
+      <c r="D51" s="56" t="n"/>
+      <c r="E51" s="56" t="n"/>
+      <c r="F51" s="57" t="n"/>
+      <c r="G51" s="22" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="16" t="n"/>
-      <c r="C52" s="49" t="n"/>
-      <c r="D52" s="50" t="n"/>
-      <c r="E52" s="50" t="n"/>
-      <c r="F52" s="51" t="n"/>
-      <c r="G52" s="16" t="n"/>
+      <c r="B52" s="22" t="n"/>
+      <c r="C52" s="55" t="n"/>
+      <c r="D52" s="56" t="n"/>
+      <c r="E52" s="56" t="n"/>
+      <c r="F52" s="57" t="n"/>
+      <c r="G52" s="22" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="16" t="n"/>
-      <c r="C53" s="49" t="n"/>
-      <c r="D53" s="50" t="n"/>
-      <c r="E53" s="50" t="n"/>
-      <c r="F53" s="51" t="n"/>
-      <c r="G53" s="16" t="n"/>
+      <c r="B53" s="22" t="n"/>
+      <c r="C53" s="55" t="n"/>
+      <c r="D53" s="56" t="n"/>
+      <c r="E53" s="56" t="n"/>
+      <c r="F53" s="57" t="n"/>
+      <c r="G53" s="22" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="16" t="n"/>
-      <c r="C54" s="49" t="n"/>
-      <c r="D54" s="50" t="n"/>
-      <c r="E54" s="50" t="n"/>
-      <c r="F54" s="51" t="n"/>
-      <c r="G54" s="16" t="n"/>
+      <c r="B54" s="22" t="n"/>
+      <c r="C54" s="55" t="n"/>
+      <c r="D54" s="56" t="n"/>
+      <c r="E54" s="56" t="n"/>
+      <c r="F54" s="57" t="n"/>
+      <c r="G54" s="22" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="16" t="n"/>
-      <c r="C55" s="49" t="n"/>
-      <c r="D55" s="50" t="n"/>
-      <c r="E55" s="50" t="n"/>
-      <c r="F55" s="51" t="n"/>
-      <c r="G55" s="16" t="n"/>
+      <c r="B55" s="22" t="n"/>
+      <c r="C55" s="55" t="n"/>
+      <c r="D55" s="56" t="n"/>
+      <c r="E55" s="56" t="n"/>
+      <c r="F55" s="57" t="n"/>
+      <c r="G55" s="22" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="16" t="n"/>
-      <c r="C56" s="49" t="n"/>
-      <c r="D56" s="50" t="n"/>
-      <c r="E56" s="50" t="n"/>
-      <c r="F56" s="51" t="n"/>
-      <c r="G56" s="16" t="n"/>
+      <c r="B56" s="22" t="n"/>
+      <c r="C56" s="55" t="n"/>
+      <c r="D56" s="56" t="n"/>
+      <c r="E56" s="56" t="n"/>
+      <c r="F56" s="57" t="n"/>
+      <c r="G56" s="22" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" s="16" t="n"/>
-      <c r="C57" s="49" t="n"/>
-      <c r="D57" s="50" t="n"/>
-      <c r="E57" s="50" t="n"/>
-      <c r="F57" s="51" t="n"/>
-      <c r="G57" s="16" t="n"/>
+      <c r="B57" s="22" t="n"/>
+      <c r="C57" s="55" t="n"/>
+      <c r="D57" s="56" t="n"/>
+      <c r="E57" s="56" t="n"/>
+      <c r="F57" s="57" t="n"/>
+      <c r="G57" s="22" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="16" t="n"/>
-      <c r="C58" s="49" t="n"/>
-      <c r="D58" s="50" t="n"/>
-      <c r="E58" s="50" t="n"/>
-      <c r="F58" s="51" t="n"/>
-      <c r="G58" s="16" t="n"/>
+      <c r="B58" s="22" t="n"/>
+      <c r="C58" s="55" t="n"/>
+      <c r="D58" s="56" t="n"/>
+      <c r="E58" s="56" t="n"/>
+      <c r="F58" s="57" t="n"/>
+      <c r="G58" s="22" t="n"/>
     </row>
     <row r="59">
-      <c r="B59" s="16" t="n"/>
-      <c r="C59" s="49" t="n"/>
-      <c r="D59" s="50" t="n"/>
-      <c r="E59" s="50" t="n"/>
-      <c r="F59" s="51" t="n"/>
-      <c r="G59" s="16" t="n"/>
+      <c r="B59" s="22" t="n"/>
+      <c r="C59" s="55" t="n"/>
+      <c r="D59" s="56" t="n"/>
+      <c r="E59" s="56" t="n"/>
+      <c r="F59" s="57" t="n"/>
+      <c r="G59" s="22" t="n"/>
     </row>
     <row r="60">
-      <c r="B60" s="16" t="n"/>
-      <c r="C60" s="49" t="n"/>
-      <c r="D60" s="50" t="n"/>
-      <c r="E60" s="50" t="n"/>
-      <c r="F60" s="51" t="n"/>
-      <c r="G60" s="16" t="n"/>
+      <c r="B60" s="22" t="n"/>
+      <c r="C60" s="55" t="n"/>
+      <c r="D60" s="56" t="n"/>
+      <c r="E60" s="56" t="n"/>
+      <c r="F60" s="57" t="n"/>
+      <c r="G60" s="22" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" s="16" t="n"/>
-      <c r="C61" s="49" t="n"/>
-      <c r="D61" s="50" t="n"/>
-      <c r="E61" s="50" t="n"/>
-      <c r="F61" s="51" t="n"/>
-      <c r="G61" s="16" t="n"/>
+      <c r="B61" s="22" t="n"/>
+      <c r="C61" s="55" t="n"/>
+      <c r="D61" s="56" t="n"/>
+      <c r="E61" s="56" t="n"/>
+      <c r="F61" s="57" t="n"/>
+      <c r="G61" s="22" t="n"/>
     </row>
     <row r="62">
-      <c r="B62" s="16" t="n"/>
-      <c r="C62" s="49" t="n"/>
-      <c r="D62" s="50" t="n"/>
-      <c r="E62" s="50" t="n"/>
-      <c r="F62" s="51" t="n"/>
-      <c r="G62" s="16" t="n"/>
+      <c r="B62" s="22" t="n"/>
+      <c r="C62" s="55" t="n"/>
+      <c r="D62" s="56" t="n"/>
+      <c r="E62" s="56" t="n"/>
+      <c r="F62" s="57" t="n"/>
+      <c r="G62" s="22" t="n"/>
     </row>
     <row r="63">
-      <c r="B63" s="16" t="n"/>
-      <c r="C63" s="49" t="n"/>
-      <c r="D63" s="50" t="n"/>
-      <c r="E63" s="50" t="n"/>
-      <c r="F63" s="51" t="n"/>
-      <c r="G63" s="16" t="n"/>
+      <c r="B63" s="22" t="n"/>
+      <c r="C63" s="55" t="n"/>
+      <c r="D63" s="56" t="n"/>
+      <c r="E63" s="56" t="n"/>
+      <c r="F63" s="57" t="n"/>
+      <c r="G63" s="22" t="n"/>
     </row>
     <row r="64">
-      <c r="B64" s="16" t="n"/>
-      <c r="C64" s="49" t="n"/>
-      <c r="D64" s="50" t="n"/>
-      <c r="E64" s="50" t="n"/>
-      <c r="F64" s="51" t="n"/>
-      <c r="G64" s="16" t="n"/>
+      <c r="B64" s="22" t="n"/>
+      <c r="C64" s="55" t="n"/>
+      <c r="D64" s="56" t="n"/>
+      <c r="E64" s="56" t="n"/>
+      <c r="F64" s="57" t="n"/>
+      <c r="G64" s="22" t="n"/>
     </row>
     <row r="65">
-      <c r="B65" s="16" t="n"/>
-      <c r="C65" s="49" t="n"/>
-      <c r="D65" s="50" t="n"/>
-      <c r="E65" s="50" t="n"/>
-      <c r="F65" s="51" t="n"/>
-      <c r="G65" s="16" t="n"/>
+      <c r="B65" s="22" t="n"/>
+      <c r="C65" s="55" t="n"/>
+      <c r="D65" s="56" t="n"/>
+      <c r="E65" s="56" t="n"/>
+      <c r="F65" s="57" t="n"/>
+      <c r="G65" s="22" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="16" t="n"/>
-      <c r="C66" s="49" t="n"/>
-      <c r="D66" s="50" t="n"/>
-      <c r="E66" s="50" t="n"/>
-      <c r="F66" s="51" t="n"/>
-      <c r="G66" s="16" t="n"/>
+      <c r="B66" s="22" t="n"/>
+      <c r="C66" s="55" t="n"/>
+      <c r="D66" s="56" t="n"/>
+      <c r="E66" s="56" t="n"/>
+      <c r="F66" s="57" t="n"/>
+      <c r="G66" s="22" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="16" t="n"/>
-      <c r="C67" s="49" t="n"/>
-      <c r="D67" s="50" t="n"/>
-      <c r="E67" s="50" t="n"/>
-      <c r="F67" s="51" t="n"/>
-      <c r="G67" s="16" t="n"/>
+      <c r="B67" s="22" t="n"/>
+      <c r="C67" s="55" t="n"/>
+      <c r="D67" s="56" t="n"/>
+      <c r="E67" s="56" t="n"/>
+      <c r="F67" s="57" t="n"/>
+      <c r="G67" s="22" t="n"/>
     </row>
     <row r="68">
-      <c r="B68" s="16" t="n"/>
-      <c r="C68" s="49" t="n"/>
-      <c r="D68" s="50" t="n"/>
-      <c r="E68" s="50" t="n"/>
-      <c r="F68" s="51" t="n"/>
-      <c r="G68" s="16" t="n"/>
+      <c r="B68" s="22" t="n"/>
+      <c r="C68" s="55" t="n"/>
+      <c r="D68" s="56" t="n"/>
+      <c r="E68" s="56" t="n"/>
+      <c r="F68" s="57" t="n"/>
+      <c r="G68" s="22" t="n"/>
     </row>
     <row r="69">
-      <c r="B69" s="16" t="n"/>
-      <c r="C69" s="49" t="n"/>
-      <c r="D69" s="50" t="n"/>
-      <c r="E69" s="50" t="n"/>
-      <c r="F69" s="51" t="n"/>
-      <c r="G69" s="16" t="n"/>
+      <c r="B69" s="22" t="n"/>
+      <c r="C69" s="55" t="n"/>
+      <c r="D69" s="56" t="n"/>
+      <c r="E69" s="56" t="n"/>
+      <c r="F69" s="57" t="n"/>
+      <c r="G69" s="22" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="16" t="n"/>
-      <c r="C70" s="49" t="n"/>
-      <c r="D70" s="50" t="n"/>
-      <c r="E70" s="50" t="n"/>
-      <c r="F70" s="51" t="n"/>
-      <c r="G70" s="16" t="n"/>
+      <c r="B70" s="22" t="n"/>
+      <c r="C70" s="55" t="n"/>
+      <c r="D70" s="56" t="n"/>
+      <c r="E70" s="56" t="n"/>
+      <c r="F70" s="57" t="n"/>
+      <c r="G70" s="22" t="n"/>
     </row>
     <row r="71">
-      <c r="B71" s="16" t="n"/>
-      <c r="C71" s="49" t="n"/>
-      <c r="D71" s="50" t="n"/>
-      <c r="E71" s="50" t="n"/>
-      <c r="F71" s="51" t="n"/>
-      <c r="G71" s="16" t="n"/>
+      <c r="B71" s="22" t="n"/>
+      <c r="C71" s="55" t="n"/>
+      <c r="D71" s="56" t="n"/>
+      <c r="E71" s="56" t="n"/>
+      <c r="F71" s="57" t="n"/>
+      <c r="G71" s="22" t="n"/>
     </row>
     <row r="72">
-      <c r="B72" s="16" t="n"/>
-      <c r="C72" s="49" t="n"/>
-      <c r="D72" s="50" t="n"/>
-      <c r="E72" s="50" t="n"/>
-      <c r="F72" s="51" t="n"/>
-      <c r="G72" s="16" t="n"/>
+      <c r="B72" s="22" t="n"/>
+      <c r="C72" s="55" t="n"/>
+      <c r="D72" s="56" t="n"/>
+      <c r="E72" s="56" t="n"/>
+      <c r="F72" s="57" t="n"/>
+      <c r="G72" s="22" t="n"/>
     </row>
     <row r="73">
-      <c r="B73" s="16" t="n"/>
-      <c r="C73" s="49" t="n"/>
-      <c r="D73" s="50" t="n"/>
-      <c r="E73" s="50" t="n"/>
-      <c r="F73" s="51" t="n"/>
-      <c r="G73" s="16" t="n"/>
+      <c r="B73" s="22" t="n"/>
+      <c r="C73" s="55" t="n"/>
+      <c r="D73" s="56" t="n"/>
+      <c r="E73" s="56" t="n"/>
+      <c r="F73" s="57" t="n"/>
+      <c r="G73" s="22" t="n"/>
     </row>
     <row r="74">
-      <c r="B74" s="16" t="n"/>
-      <c r="C74" s="49" t="n"/>
-      <c r="D74" s="50" t="n"/>
-      <c r="E74" s="50" t="n"/>
-      <c r="F74" s="51" t="n"/>
-      <c r="G74" s="16" t="n"/>
+      <c r="B74" s="22" t="n"/>
+      <c r="C74" s="55" t="n"/>
+      <c r="D74" s="56" t="n"/>
+      <c r="E74" s="56" t="n"/>
+      <c r="F74" s="57" t="n"/>
+      <c r="G74" s="22" t="n"/>
     </row>
     <row r="75">
-      <c r="B75" s="16" t="n"/>
-      <c r="C75" s="49" t="n"/>
-      <c r="D75" s="50" t="n"/>
-      <c r="E75" s="50" t="n"/>
-      <c r="F75" s="51" t="n"/>
-      <c r="G75" s="16" t="n"/>
+      <c r="B75" s="22" t="n"/>
+      <c r="C75" s="55" t="n"/>
+      <c r="D75" s="56" t="n"/>
+      <c r="E75" s="56" t="n"/>
+      <c r="F75" s="57" t="n"/>
+      <c r="G75" s="22" t="n"/>
     </row>
     <row r="76">
-      <c r="B76" s="16" t="n"/>
-      <c r="C76" s="49" t="n"/>
-      <c r="D76" s="50" t="n"/>
-      <c r="E76" s="50" t="n"/>
-      <c r="F76" s="51" t="n"/>
-      <c r="G76" s="16" t="n"/>
+      <c r="B76" s="22" t="n"/>
+      <c r="C76" s="55" t="n"/>
+      <c r="D76" s="56" t="n"/>
+      <c r="E76" s="56" t="n"/>
+      <c r="F76" s="57" t="n"/>
+      <c r="G76" s="22" t="n"/>
     </row>
     <row r="77">
-      <c r="B77" s="16" t="n"/>
-      <c r="C77" s="49" t="n"/>
-      <c r="D77" s="50" t="n"/>
-      <c r="E77" s="50" t="n"/>
-      <c r="F77" s="51" t="n"/>
-      <c r="G77" s="16" t="n"/>
+      <c r="B77" s="22" t="n"/>
+      <c r="C77" s="55" t="n"/>
+      <c r="D77" s="56" t="n"/>
+      <c r="E77" s="56" t="n"/>
+      <c r="F77" s="57" t="n"/>
+      <c r="G77" s="22" t="n"/>
     </row>
     <row r="78">
-      <c r="B78" s="16" t="n"/>
-      <c r="C78" s="49" t="n"/>
-      <c r="D78" s="50" t="n"/>
-      <c r="E78" s="50" t="n"/>
-      <c r="F78" s="51" t="n"/>
-      <c r="G78" s="16" t="n"/>
+      <c r="B78" s="22" t="n"/>
+      <c r="C78" s="55" t="n"/>
+      <c r="D78" s="56" t="n"/>
+      <c r="E78" s="56" t="n"/>
+      <c r="F78" s="57" t="n"/>
+      <c r="G78" s="22" t="n"/>
     </row>
     <row r="79">
-      <c r="B79" s="16" t="n"/>
-      <c r="C79" s="49" t="n"/>
-      <c r="D79" s="50" t="n"/>
-      <c r="E79" s="50" t="n"/>
-      <c r="F79" s="51" t="n"/>
-      <c r="G79" s="16" t="n"/>
+      <c r="B79" s="22" t="n"/>
+      <c r="C79" s="55" t="n"/>
+      <c r="D79" s="56" t="n"/>
+      <c r="E79" s="56" t="n"/>
+      <c r="F79" s="57" t="n"/>
+      <c r="G79" s="22" t="n"/>
     </row>
     <row r="80">
-      <c r="B80" s="16" t="n"/>
-      <c r="C80" s="49" t="n"/>
-      <c r="D80" s="50" t="n"/>
-      <c r="E80" s="50" t="n"/>
-      <c r="F80" s="51" t="n"/>
-      <c r="G80" s="16" t="n"/>
+      <c r="B80" s="22" t="n"/>
+      <c r="C80" s="55" t="n"/>
+      <c r="D80" s="56" t="n"/>
+      <c r="E80" s="56" t="n"/>
+      <c r="F80" s="57" t="n"/>
+      <c r="G80" s="22" t="n"/>
     </row>
     <row r="81">
-      <c r="B81" s="16" t="n"/>
-      <c r="C81" s="49" t="n"/>
-      <c r="D81" s="50" t="n"/>
-      <c r="E81" s="50" t="n"/>
-      <c r="F81" s="51" t="n"/>
-      <c r="G81" s="16" t="n"/>
+      <c r="B81" s="22" t="n"/>
+      <c r="C81" s="55" t="n"/>
+      <c r="D81" s="56" t="n"/>
+      <c r="E81" s="56" t="n"/>
+      <c r="F81" s="57" t="n"/>
+      <c r="G81" s="22" t="n"/>
     </row>
     <row r="82">
-      <c r="B82" s="16" t="n"/>
-      <c r="C82" s="49" t="n"/>
-      <c r="D82" s="50" t="n"/>
-      <c r="E82" s="50" t="n"/>
-      <c r="F82" s="51" t="n"/>
-      <c r="G82" s="16" t="n"/>
+      <c r="B82" s="22" t="n"/>
+      <c r="C82" s="55" t="n"/>
+      <c r="D82" s="56" t="n"/>
+      <c r="E82" s="56" t="n"/>
+      <c r="F82" s="57" t="n"/>
+      <c r="G82" s="22" t="n"/>
     </row>
     <row r="83">
-      <c r="B83" s="16" t="n"/>
-      <c r="C83" s="49" t="n"/>
-      <c r="D83" s="50" t="n"/>
-      <c r="E83" s="50" t="n"/>
-      <c r="F83" s="51" t="n"/>
-      <c r="G83" s="16" t="n"/>
+      <c r="B83" s="22" t="n"/>
+      <c r="C83" s="55" t="n"/>
+      <c r="D83" s="56" t="n"/>
+      <c r="E83" s="56" t="n"/>
+      <c r="F83" s="57" t="n"/>
+      <c r="G83" s="22" t="n"/>
     </row>
     <row r="84">
-      <c r="B84" s="16" t="n"/>
-      <c r="C84" s="49" t="n"/>
-      <c r="D84" s="50" t="n"/>
-      <c r="E84" s="50" t="n"/>
-      <c r="F84" s="51" t="n"/>
-      <c r="G84" s="16" t="n"/>
+      <c r="B84" s="22" t="n"/>
+      <c r="C84" s="55" t="n"/>
+      <c r="D84" s="56" t="n"/>
+      <c r="E84" s="56" t="n"/>
+      <c r="F84" s="57" t="n"/>
+      <c r="G84" s="22" t="n"/>
     </row>
     <row r="85">
-      <c r="B85" s="16" t="n"/>
-      <c r="C85" s="49" t="n"/>
-      <c r="D85" s="50" t="n"/>
-      <c r="E85" s="50" t="n"/>
-      <c r="F85" s="51" t="n"/>
-      <c r="G85" s="16" t="n"/>
+      <c r="B85" s="22" t="n"/>
+      <c r="C85" s="55" t="n"/>
+      <c r="D85" s="56" t="n"/>
+      <c r="E85" s="56" t="n"/>
+      <c r="F85" s="57" t="n"/>
+      <c r="G85" s="22" t="n"/>
     </row>
     <row r="86">
-      <c r="B86" s="16" t="n"/>
-      <c r="C86" s="49" t="n"/>
-      <c r="D86" s="50" t="n"/>
-      <c r="E86" s="50" t="n"/>
-      <c r="F86" s="51" t="n"/>
-      <c r="G86" s="16" t="n"/>
+      <c r="B86" s="22" t="n"/>
+      <c r="C86" s="55" t="n"/>
+      <c r="D86" s="56" t="n"/>
+      <c r="E86" s="56" t="n"/>
+      <c r="F86" s="57" t="n"/>
+      <c r="G86" s="22" t="n"/>
     </row>
     <row r="87">
-      <c r="B87" s="16" t="n"/>
-      <c r="C87" s="49" t="n"/>
-      <c r="D87" s="50" t="n"/>
-      <c r="E87" s="50" t="n"/>
-      <c r="F87" s="51" t="n"/>
-      <c r="G87" s="16" t="n"/>
+      <c r="B87" s="22" t="n"/>
+      <c r="C87" s="55" t="n"/>
+      <c r="D87" s="56" t="n"/>
+      <c r="E87" s="56" t="n"/>
+      <c r="F87" s="57" t="n"/>
+      <c r="G87" s="22" t="n"/>
     </row>
     <row r="88">
-      <c r="B88" s="16" t="n"/>
-      <c r="C88" s="49" t="n"/>
-      <c r="D88" s="50" t="n"/>
-      <c r="E88" s="50" t="n"/>
-      <c r="F88" s="51" t="n"/>
-      <c r="G88" s="16" t="n"/>
+      <c r="B88" s="22" t="n"/>
+      <c r="C88" s="55" t="n"/>
+      <c r="D88" s="56" t="n"/>
+      <c r="E88" s="56" t="n"/>
+      <c r="F88" s="57" t="n"/>
+      <c r="G88" s="22" t="n"/>
     </row>
     <row r="89">
-      <c r="B89" s="16" t="n"/>
-      <c r="C89" s="49" t="n"/>
-      <c r="D89" s="50" t="n"/>
-      <c r="E89" s="50" t="n"/>
-      <c r="F89" s="51" t="n"/>
-      <c r="G89" s="16" t="n"/>
+      <c r="B89" s="22" t="n"/>
+      <c r="C89" s="55" t="n"/>
+      <c r="D89" s="56" t="n"/>
+      <c r="E89" s="56" t="n"/>
+      <c r="F89" s="57" t="n"/>
+      <c r="G89" s="22" t="n"/>
     </row>
     <row r="90">
-      <c r="B90" s="16" t="n"/>
-      <c r="C90" s="49" t="n"/>
-      <c r="D90" s="50" t="n"/>
-      <c r="E90" s="50" t="n"/>
-      <c r="F90" s="51" t="n"/>
-      <c r="G90" s="16" t="n"/>
+      <c r="B90" s="22" t="n"/>
+      <c r="C90" s="55" t="n"/>
+      <c r="D90" s="56" t="n"/>
+      <c r="E90" s="56" t="n"/>
+      <c r="F90" s="57" t="n"/>
+      <c r="G90" s="22" t="n"/>
     </row>
     <row r="91">
-      <c r="B91" s="16" t="n"/>
-      <c r="C91" s="49" t="n"/>
-      <c r="D91" s="50" t="n"/>
-      <c r="E91" s="50" t="n"/>
-      <c r="F91" s="51" t="n"/>
-      <c r="G91" s="16" t="n"/>
+      <c r="B91" s="22" t="n"/>
+      <c r="C91" s="55" t="n"/>
+      <c r="D91" s="56" t="n"/>
+      <c r="E91" s="56" t="n"/>
+      <c r="F91" s="57" t="n"/>
+      <c r="G91" s="22" t="n"/>
     </row>
     <row r="92">
-      <c r="B92" s="16" t="n"/>
-      <c r="C92" s="49" t="n"/>
-      <c r="D92" s="50" t="n"/>
-      <c r="E92" s="50" t="n"/>
-      <c r="F92" s="51" t="n"/>
-      <c r="G92" s="16" t="n"/>
+      <c r="B92" s="22" t="n"/>
+      <c r="C92" s="55" t="n"/>
+      <c r="D92" s="56" t="n"/>
+      <c r="E92" s="56" t="n"/>
+      <c r="F92" s="57" t="n"/>
+      <c r="G92" s="22" t="n"/>
     </row>
     <row r="93">
-      <c r="B93" s="16" t="n"/>
-      <c r="C93" s="49" t="n"/>
-      <c r="D93" s="50" t="n"/>
-      <c r="E93" s="50" t="n"/>
-      <c r="F93" s="51" t="n"/>
-      <c r="G93" s="16" t="n"/>
+      <c r="B93" s="22" t="n"/>
+      <c r="C93" s="55" t="n"/>
+      <c r="D93" s="56" t="n"/>
+      <c r="E93" s="56" t="n"/>
+      <c r="F93" s="57" t="n"/>
+      <c r="G93" s="22" t="n"/>
     </row>
     <row r="94">
-      <c r="B94" s="16" t="n"/>
-      <c r="C94" s="49" t="n"/>
-      <c r="D94" s="50" t="n"/>
-      <c r="E94" s="50" t="n"/>
-      <c r="F94" s="51" t="n"/>
-      <c r="G94" s="16" t="n"/>
+      <c r="B94" s="22" t="n"/>
+      <c r="C94" s="55" t="n"/>
+      <c r="D94" s="56" t="n"/>
+      <c r="E94" s="56" t="n"/>
+      <c r="F94" s="57" t="n"/>
+      <c r="G94" s="22" t="n"/>
     </row>
     <row r="95">
-      <c r="B95" s="16" t="n"/>
-      <c r="C95" s="49" t="n"/>
-      <c r="D95" s="50" t="n"/>
-      <c r="E95" s="50" t="n"/>
-      <c r="F95" s="51" t="n"/>
-      <c r="G95" s="16" t="n"/>
+      <c r="B95" s="22" t="n"/>
+      <c r="C95" s="55" t="n"/>
+      <c r="D95" s="56" t="n"/>
+      <c r="E95" s="56" t="n"/>
+      <c r="F95" s="57" t="n"/>
+      <c r="G95" s="22" t="n"/>
     </row>
     <row r="96">
-      <c r="B96" s="16" t="n"/>
-      <c r="C96" s="49" t="n"/>
-      <c r="D96" s="50" t="n"/>
-      <c r="E96" s="50" t="n"/>
-      <c r="F96" s="51" t="n"/>
-      <c r="G96" s="16" t="n"/>
+      <c r="B96" s="22" t="n"/>
+      <c r="C96" s="55" t="n"/>
+      <c r="D96" s="56" t="n"/>
+      <c r="E96" s="56" t="n"/>
+      <c r="F96" s="57" t="n"/>
+      <c r="G96" s="22" t="n"/>
     </row>
     <row r="97">
-      <c r="B97" s="16" t="n"/>
-      <c r="C97" s="49" t="n"/>
-      <c r="D97" s="50" t="n"/>
-      <c r="E97" s="50" t="n"/>
-      <c r="F97" s="51" t="n"/>
-      <c r="G97" s="16" t="n"/>
+      <c r="B97" s="22" t="n"/>
+      <c r="C97" s="55" t="n"/>
+      <c r="D97" s="56" t="n"/>
+      <c r="E97" s="56" t="n"/>
+      <c r="F97" s="57" t="n"/>
+      <c r="G97" s="22" t="n"/>
     </row>
     <row r="98">
-      <c r="B98" s="16" t="n"/>
-      <c r="C98" s="49" t="n"/>
-      <c r="D98" s="50" t="n"/>
-      <c r="E98" s="50" t="n"/>
-      <c r="F98" s="51" t="n"/>
-      <c r="G98" s="16" t="n"/>
+      <c r="B98" s="22" t="n"/>
+      <c r="C98" s="55" t="n"/>
+      <c r="D98" s="56" t="n"/>
+      <c r="E98" s="56" t="n"/>
+      <c r="F98" s="57" t="n"/>
+      <c r="G98" s="22" t="n"/>
     </row>
     <row r="99">
-      <c r="B99" s="16" t="n"/>
-      <c r="C99" s="49" t="n"/>
-      <c r="D99" s="50" t="n"/>
-      <c r="E99" s="50" t="n"/>
-      <c r="F99" s="51" t="n"/>
-      <c r="G99" s="16" t="n"/>
+      <c r="B99" s="22" t="n"/>
+      <c r="C99" s="55" t="n"/>
+      <c r="D99" s="56" t="n"/>
+      <c r="E99" s="56" t="n"/>
+      <c r="F99" s="57" t="n"/>
+      <c r="G99" s="22" t="n"/>
     </row>
     <row r="100">
-      <c r="B100" s="16" t="n"/>
-      <c r="C100" s="49" t="n"/>
-      <c r="D100" s="50" t="n"/>
-      <c r="E100" s="50" t="n"/>
-      <c r="F100" s="51" t="n"/>
-      <c r="G100" s="16" t="n"/>
+      <c r="B100" s="22" t="n"/>
+      <c r="C100" s="55" t="n"/>
+      <c r="D100" s="56" t="n"/>
+      <c r="E100" s="56" t="n"/>
+      <c r="F100" s="57" t="n"/>
+      <c r="G100" s="22" t="n"/>
     </row>
     <row r="101">
-      <c r="B101" s="16" t="n"/>
-      <c r="C101" s="49" t="n"/>
-      <c r="D101" s="50" t="n"/>
-      <c r="E101" s="50" t="n"/>
-      <c r="F101" s="51" t="n"/>
-      <c r="G101" s="16" t="n"/>
+      <c r="B101" s="22" t="n"/>
+      <c r="C101" s="55" t="n"/>
+      <c r="D101" s="56" t="n"/>
+      <c r="E101" s="56" t="n"/>
+      <c r="F101" s="57" t="n"/>
+      <c r="G101" s="22" t="n"/>
     </row>
     <row r="102">
-      <c r="B102" s="16" t="n"/>
-      <c r="C102" s="49" t="n"/>
-      <c r="D102" s="50" t="n"/>
-      <c r="E102" s="50" t="n"/>
-      <c r="F102" s="51" t="n"/>
-      <c r="G102" s="16" t="n"/>
+      <c r="B102" s="22" t="n"/>
+      <c r="C102" s="55" t="n"/>
+      <c r="D102" s="56" t="n"/>
+      <c r="E102" s="56" t="n"/>
+      <c r="F102" s="57" t="n"/>
+      <c r="G102" s="22" t="n"/>
     </row>
     <row r="103">
-      <c r="B103" s="16" t="n"/>
-      <c r="C103" s="49" t="n"/>
-      <c r="D103" s="50" t="n"/>
-      <c r="E103" s="50" t="n"/>
-      <c r="F103" s="51" t="n"/>
-      <c r="G103" s="16" t="n"/>
+      <c r="B103" s="22" t="n"/>
+      <c r="C103" s="55" t="n"/>
+      <c r="D103" s="56" t="n"/>
+      <c r="E103" s="56" t="n"/>
+      <c r="F103" s="57" t="n"/>
+      <c r="G103" s="22" t="n"/>
     </row>
     <row r="104">
-      <c r="B104" s="16" t="n"/>
-      <c r="C104" s="49" t="n"/>
-      <c r="D104" s="50" t="n"/>
-      <c r="E104" s="50" t="n"/>
-      <c r="F104" s="51" t="n"/>
-      <c r="G104" s="16" t="n"/>
+      <c r="B104" s="22" t="n"/>
+      <c r="C104" s="55" t="n"/>
+      <c r="D104" s="56" t="n"/>
+      <c r="E104" s="56" t="n"/>
+      <c r="F104" s="57" t="n"/>
+      <c r="G104" s="22" t="n"/>
     </row>
     <row r="105">
-      <c r="B105" s="16" t="n"/>
-      <c r="C105" s="49" t="n"/>
-      <c r="D105" s="50" t="n"/>
-      <c r="E105" s="50" t="n"/>
-      <c r="F105" s="51" t="n"/>
-      <c r="G105" s="16" t="n"/>
+      <c r="B105" s="22" t="n"/>
+      <c r="C105" s="55" t="n"/>
+      <c r="D105" s="56" t="n"/>
+      <c r="E105" s="56" t="n"/>
+      <c r="F105" s="57" t="n"/>
+      <c r="G105" s="22" t="n"/>
     </row>
     <row r="106">
-      <c r="B106" s="16" t="n"/>
-      <c r="C106" s="49" t="n"/>
-      <c r="D106" s="50" t="n"/>
-      <c r="E106" s="50" t="n"/>
-      <c r="F106" s="51" t="n"/>
-      <c r="G106" s="16" t="n"/>
+      <c r="B106" s="22" t="n"/>
+      <c r="C106" s="55" t="n"/>
+      <c r="D106" s="56" t="n"/>
+      <c r="E106" s="56" t="n"/>
+      <c r="F106" s="57" t="n"/>
+      <c r="G106" s="22" t="n"/>
     </row>
     <row r="107">
-      <c r="B107" s="16" t="n"/>
-      <c r="C107" s="49" t="n"/>
-      <c r="D107" s="50" t="n"/>
-      <c r="E107" s="50" t="n"/>
-      <c r="F107" s="51" t="n"/>
-      <c r="G107" s="16" t="n"/>
+      <c r="B107" s="22" t="n"/>
+      <c r="C107" s="55" t="n"/>
+      <c r="D107" s="56" t="n"/>
+      <c r="E107" s="56" t="n"/>
+      <c r="F107" s="57" t="n"/>
+      <c r="G107" s="22" t="n"/>
     </row>
     <row r="109" ht="8" customHeight="1">
-      <c r="B109" s="34" t="n"/>
+      <c r="B109" s="40" t="n"/>
     </row>
     <row r="110" ht="16" customHeight="1">
-      <c r="B110" s="35" t="inlineStr">
+      <c r="B110" s="41" t="inlineStr">
         <is>
           <t>MIX SHOP DIGITAL  ·  Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
     </row>
     <row r="111" ht="16" customHeight="1">
-      <c r="B111" s="36" t="inlineStr">
+      <c r="B111" s="42" t="inlineStr">
         <is>
           <t>Versión gratuita  ·  Para gestionar todo tu negocio en un solo lugar, conocé Mi Negocio PY  →  mixshopdigital.com.py</t>
         </is>
@@ -3131,8 +3363,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="8CA3"/>
   <autoFilter ref="B7:G107"/>
-  <mergeCells count="12">
-    <mergeCell ref="B3:G3"/>
+  <mergeCells count="11">
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="B111:G111"/>
@@ -3192,6 +3423,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3220,127 +3452,144 @@
     <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>MIX SHOP DIGITAL</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
+    <row r="1" ht="38" customHeight="1">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>PANEL</t>
         </is>
       </c>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Tus presupuestos de un vistazo</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="4" customHeight="1">
-      <c r="B3" s="5" t="n"/>
+    <row r="3" ht="5" customHeight="1">
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="9" t="n"/>
+      <c r="H3" s="9" t="n"/>
+      <c r="I3" s="9" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="11" t="n"/>
+      <c r="M3" s="11" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>← VOLVER</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>El panel se arma solo con lo que anotás en HISTORIAL. No hace falta escribir nada acá.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="52" t="inlineStr">
+      <c r="B5" s="58" t="inlineStr">
         <is>
           <t>+ Anotar presupuesto</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Presupuesto</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>Ajustes</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>Ayuda</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="6">
+      <c r="B6" s="12">
         <f>"Año de control: "&amp;AnioCtl&amp;"   ·   "&amp;NombreNegocio</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="B8" s="53" t="inlineStr">
+      <c r="B8" s="59" t="inlineStr">
         <is>
           <t>PRESUPUESTADO</t>
         </is>
       </c>
-      <c r="E8" s="54" t="inlineStr">
+      <c r="E8" s="60" t="inlineStr">
         <is>
           <t>POR COBRAR (aprobado)</t>
         </is>
       </c>
-      <c r="H8" s="55" t="inlineStr">
+      <c r="H8" s="61" t="inlineStr">
         <is>
           <t>COBRADO</t>
         </is>
       </c>
-      <c r="K8" s="56" t="inlineStr">
+      <c r="K8" s="62" t="inlineStr">
         <is>
           <t>TASA DE ÉXITO</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="B9" s="57">
+      <c r="B9" s="63">
         <f>E21</f>
         <v/>
       </c>
-      <c r="E9" s="58">
+      <c r="E9" s="64">
         <f>E17</f>
         <v/>
       </c>
-      <c r="H9" s="59">
+      <c r="H9" s="65">
         <f>E18</f>
         <v/>
       </c>
-      <c r="K9" s="60">
+      <c r="K9" s="66">
         <f>IF((D17+D18+D19)=0,0,(D17+D18)/(D17+D18+D19))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="61">
+      <c r="B10" s="67">
         <f>Moneda</f>
         <v/>
       </c>
-      <c r="E10" s="62">
+      <c r="E10" s="68">
         <f>Moneda</f>
         <v/>
       </c>
-      <c r="H10" s="63">
+      <c r="H10" s="69">
         <f>Moneda</f>
         <v/>
       </c>
-      <c r="K10" s="64" t="inlineStr">
+      <c r="K10" s="70" t="inlineStr">
         <is>
           <t>aprobados ÷ respondidos</t>
         </is>
@@ -3348,424 +3597,424 @@
     </row>
     <row r="11" ht="8" customHeight="1"/>
     <row r="12" ht="24" customHeight="1">
-      <c r="B12" s="65">
+      <c r="B12" s="71">
         <f>IF(E21=0,"Anotá tus presupuestos en la hoja HISTORIAL para ver tu panel.",IF(E17&gt;0,"⚠ Tenés "&amp;FIXED(E17,Decimales)&amp;" "&amp;Moneda&amp;" aprobados esperando que los cobres.",IF(D16&gt;0,"✔ Todo lo aprobado está cobrado. Te quedan "&amp;D16&amp;" presupuesto(s) esperando respuesta.","✔ Todo lo aprobado está cobrado.")))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="38" t="inlineStr">
+      <c r="B14" s="44" t="inlineStr">
         <is>
           <t>POR ESTADO (año elegido)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="66" t="inlineStr">
+      <c r="B15" s="72" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="D15" s="66" t="inlineStr">
+      <c r="D15" s="72" t="inlineStr">
         <is>
           <t>Cant.</t>
         </is>
       </c>
-      <c r="E15" s="66" t="inlineStr">
+      <c r="E15" s="72" t="inlineStr">
         <is>
           <t>Monto</t>
         </is>
       </c>
-      <c r="F15" s="66" t="inlineStr">
+      <c r="F15" s="72" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="B16" s="67" t="inlineStr">
+      <c r="B16" s="73" t="inlineStr">
         <is>
           <t>Enviado</t>
         </is>
       </c>
-      <c r="D16" s="68">
+      <c r="D16" s="74">
         <f>COUNTIFS(HISTORIAL!$G$8:$G$107,B16,HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,1,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl+1,1,1))</f>
         <v/>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="28">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$G$8:$G$107,B16,HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,1,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl+1,1,1))</f>
         <v/>
       </c>
-      <c r="F16" s="69">
+      <c r="F16" s="75">
         <f>IF($E$21=0,0,E16/$E$21)</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="B17" s="67" t="inlineStr">
+      <c r="B17" s="73" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="D17" s="68">
+      <c r="D17" s="74">
         <f>COUNTIFS(HISTORIAL!$G$8:$G$107,B17,HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,1,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl+1,1,1))</f>
         <v/>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="28">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$G$8:$G$107,B17,HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,1,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl+1,1,1))</f>
         <v/>
       </c>
-      <c r="F17" s="69">
+      <c r="F17" s="75">
         <f>IF($E$21=0,0,E17/$E$21)</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="B18" s="67" t="inlineStr">
+      <c r="B18" s="73" t="inlineStr">
         <is>
           <t>Cobrado</t>
         </is>
       </c>
-      <c r="D18" s="68">
+      <c r="D18" s="74">
         <f>COUNTIFS(HISTORIAL!$G$8:$G$107,B18,HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,1,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl+1,1,1))</f>
         <v/>
       </c>
-      <c r="E18" s="22">
+      <c r="E18" s="28">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$G$8:$G$107,B18,HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,1,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl+1,1,1))</f>
         <v/>
       </c>
-      <c r="F18" s="69">
+      <c r="F18" s="75">
         <f>IF($E$21=0,0,E18/$E$21)</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="B19" s="67" t="inlineStr">
+      <c r="B19" s="73" t="inlineStr">
         <is>
           <t>Rechazado</t>
         </is>
       </c>
-      <c r="D19" s="68">
+      <c r="D19" s="74">
         <f>COUNTIFS(HISTORIAL!$G$8:$G$107,B19,HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,1,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl+1,1,1))</f>
         <v/>
       </c>
-      <c r="E19" s="22">
+      <c r="E19" s="28">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$G$8:$G$107,B19,HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,1,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl+1,1,1))</f>
         <v/>
       </c>
-      <c r="F19" s="69">
+      <c r="F19" s="75">
         <f>IF($E$21=0,0,E19/$E$21)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="6" customHeight="1"/>
     <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="70" t="inlineStr">
+      <c r="B21" s="76" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D21" s="71">
+      <c r="D21" s="77">
         <f>SUM(D16:D19)</f>
         <v/>
       </c>
-      <c r="E21" s="72">
+      <c r="E21" s="78">
         <f>SUM(E16:E19)</f>
         <v/>
       </c>
-      <c r="F21" s="73">
+      <c r="F21" s="79">
         <f>SUM(F16:F19)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="41" t="inlineStr">
+      <c r="B23" s="47" t="inlineStr">
         <is>
           <t>MES A MES</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="B24" s="74" t="inlineStr">
+      <c r="B24" s="80" t="inlineStr">
         <is>
           <t>Mes</t>
         </is>
       </c>
-      <c r="C24" s="74" t="inlineStr">
+      <c r="C24" s="80" t="inlineStr">
         <is>
           <t>Cant.</t>
         </is>
       </c>
-      <c r="D24" s="74" t="inlineStr">
+      <c r="D24" s="80" t="inlineStr">
         <is>
           <t>Presup.</t>
         </is>
       </c>
-      <c r="E24" s="74" t="inlineStr">
+      <c r="E24" s="80" t="inlineStr">
         <is>
           <t>Cobrado</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="67" t="inlineStr">
+      <c r="B25" s="73" t="inlineStr">
         <is>
           <t>Enero</t>
         </is>
       </c>
-      <c r="C25" s="75">
+      <c r="C25" s="81">
         <f>COUNTIFS(HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,1,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,2,1))</f>
         <v/>
       </c>
-      <c r="D25" s="76">
+      <c r="D25" s="82">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,1,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,2,1))</f>
         <v/>
       </c>
-      <c r="E25" s="76">
+      <c r="E25" s="82">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$G$8:$G$107,"Cobrado",HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,1,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,2,1))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="77" t="inlineStr">
+      <c r="B26" s="83" t="inlineStr">
         <is>
           <t>Febrero</t>
         </is>
       </c>
-      <c r="C26" s="78">
+      <c r="C26" s="84">
         <f>COUNTIFS(HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,2,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,3,1))</f>
         <v/>
       </c>
-      <c r="D26" s="79">
+      <c r="D26" s="85">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,2,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,3,1))</f>
         <v/>
       </c>
-      <c r="E26" s="79">
+      <c r="E26" s="85">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$G$8:$G$107,"Cobrado",HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,2,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,3,1))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="B27" s="67" t="inlineStr">
+      <c r="B27" s="73" t="inlineStr">
         <is>
           <t>Marzo</t>
         </is>
       </c>
-      <c r="C27" s="75">
+      <c r="C27" s="81">
         <f>COUNTIFS(HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,3,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,4,1))</f>
         <v/>
       </c>
-      <c r="D27" s="76">
+      <c r="D27" s="82">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,3,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,4,1))</f>
         <v/>
       </c>
-      <c r="E27" s="76">
+      <c r="E27" s="82">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$G$8:$G$107,"Cobrado",HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,3,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,4,1))</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="B28" s="77" t="inlineStr">
+      <c r="B28" s="83" t="inlineStr">
         <is>
           <t>Abril</t>
         </is>
       </c>
-      <c r="C28" s="78">
+      <c r="C28" s="84">
         <f>COUNTIFS(HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,4,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,5,1))</f>
         <v/>
       </c>
-      <c r="D28" s="79">
+      <c r="D28" s="85">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,4,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,5,1))</f>
         <v/>
       </c>
-      <c r="E28" s="79">
+      <c r="E28" s="85">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$G$8:$G$107,"Cobrado",HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,4,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,5,1))</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="67" t="inlineStr">
+      <c r="B29" s="73" t="inlineStr">
         <is>
           <t>Mayo</t>
         </is>
       </c>
-      <c r="C29" s="75">
+      <c r="C29" s="81">
         <f>COUNTIFS(HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,5,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,6,1))</f>
         <v/>
       </c>
-      <c r="D29" s="76">
+      <c r="D29" s="82">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,5,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,6,1))</f>
         <v/>
       </c>
-      <c r="E29" s="76">
+      <c r="E29" s="82">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$G$8:$G$107,"Cobrado",HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,5,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,6,1))</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="77" t="inlineStr">
+      <c r="B30" s="83" t="inlineStr">
         <is>
           <t>Junio</t>
         </is>
       </c>
-      <c r="C30" s="78">
+      <c r="C30" s="84">
         <f>COUNTIFS(HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,6,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,7,1))</f>
         <v/>
       </c>
-      <c r="D30" s="79">
+      <c r="D30" s="85">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,6,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,7,1))</f>
         <v/>
       </c>
-      <c r="E30" s="79">
+      <c r="E30" s="85">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$G$8:$G$107,"Cobrado",HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,6,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,7,1))</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="B31" s="67" t="inlineStr">
+      <c r="B31" s="73" t="inlineStr">
         <is>
           <t>Julio</t>
         </is>
       </c>
-      <c r="C31" s="75">
+      <c r="C31" s="81">
         <f>COUNTIFS(HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,7,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,8,1))</f>
         <v/>
       </c>
-      <c r="D31" s="76">
+      <c r="D31" s="82">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,7,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,8,1))</f>
         <v/>
       </c>
-      <c r="E31" s="76">
+      <c r="E31" s="82">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$G$8:$G$107,"Cobrado",HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,7,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,8,1))</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="B32" s="77" t="inlineStr">
+      <c r="B32" s="83" t="inlineStr">
         <is>
           <t>Agosto</t>
         </is>
       </c>
-      <c r="C32" s="78">
+      <c r="C32" s="84">
         <f>COUNTIFS(HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,8,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,9,1))</f>
         <v/>
       </c>
-      <c r="D32" s="79">
+      <c r="D32" s="85">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,8,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,9,1))</f>
         <v/>
       </c>
-      <c r="E32" s="79">
+      <c r="E32" s="85">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$G$8:$G$107,"Cobrado",HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,8,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,9,1))</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="B33" s="67" t="inlineStr">
+      <c r="B33" s="73" t="inlineStr">
         <is>
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="C33" s="75">
+      <c r="C33" s="81">
         <f>COUNTIFS(HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,9,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,10,1))</f>
         <v/>
       </c>
-      <c r="D33" s="76">
+      <c r="D33" s="82">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,9,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,10,1))</f>
         <v/>
       </c>
-      <c r="E33" s="76">
+      <c r="E33" s="82">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$G$8:$G$107,"Cobrado",HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,9,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,10,1))</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="B34" s="77" t="inlineStr">
+      <c r="B34" s="83" t="inlineStr">
         <is>
           <t>Octubre</t>
         </is>
       </c>
-      <c r="C34" s="78">
+      <c r="C34" s="84">
         <f>COUNTIFS(HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,10,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,11,1))</f>
         <v/>
       </c>
-      <c r="D34" s="79">
+      <c r="D34" s="85">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,10,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,11,1))</f>
         <v/>
       </c>
-      <c r="E34" s="79">
+      <c r="E34" s="85">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$G$8:$G$107,"Cobrado",HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,10,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,11,1))</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="67" t="inlineStr">
+      <c r="B35" s="73" t="inlineStr">
         <is>
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="C35" s="75">
+      <c r="C35" s="81">
         <f>COUNTIFS(HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,11,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,12,1))</f>
         <v/>
       </c>
-      <c r="D35" s="76">
+      <c r="D35" s="82">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,11,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,12,1))</f>
         <v/>
       </c>
-      <c r="E35" s="76">
+      <c r="E35" s="82">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$G$8:$G$107,"Cobrado",HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,11,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,12,1))</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="77" t="inlineStr">
+      <c r="B36" s="83" t="inlineStr">
         <is>
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="C36" s="78">
+      <c r="C36" s="84">
         <f>COUNTIFS(HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,12,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,13,1))</f>
         <v/>
       </c>
-      <c r="D36" s="79">
+      <c r="D36" s="85">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,12,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,13,1))</f>
         <v/>
       </c>
-      <c r="E36" s="79">
+      <c r="E36" s="85">
         <f>SUMIFS(HISTORIAL!$F$8:$F$107,HISTORIAL!$G$8:$G$107,"Cobrado",HISTORIAL!$C$8:$C$107,"&gt;="&amp;DATE(AnioCtl,12,1),HISTORIAL!$C$8:$C$107,"&lt;"&amp;DATE(AnioCtl,13,1))</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="B37" s="80" t="inlineStr">
+      <c r="B37" s="86" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C37" s="81">
+      <c r="C37" s="87">
         <f>SUM(C25:C36)</f>
         <v/>
       </c>
-      <c r="D37" s="82">
+      <c r="D37" s="88">
         <f>SUM(D25:D36)</f>
         <v/>
       </c>
-      <c r="E37" s="82">
+      <c r="E37" s="88">
         <f>SUM(E25:E36)</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="8" customHeight="1">
-      <c r="B47" s="34" t="n"/>
+      <c r="B47" s="40" t="n"/>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="B48" s="35" t="inlineStr">
+      <c r="B48" s="41" t="inlineStr">
         <is>
           <t>MIX SHOP DIGITAL  ·  Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="B49" s="36" t="inlineStr">
+      <c r="B49" s="42" t="inlineStr">
         <is>
           <t>Versión gratuita  ·  Para gestionar todo tu negocio en un solo lugar, conocé Mi Negocio PY  →  mixshopdigital.com.py</t>
         </is>
@@ -3773,7 +4022,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8CA3"/>
-  <mergeCells count="35">
+  <mergeCells count="34">
     <mergeCell ref="E10:G10"/>
     <mergeCell ref="B48:M48"/>
     <mergeCell ref="B16:C16"/>
@@ -3803,7 +4052,6 @@
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="H10:J10"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B3:M3"/>
     <mergeCell ref="K9:M9"/>
     <mergeCell ref="E8:G8"/>
     <mergeCell ref="H9:J9"/>
@@ -3878,220 +4126,219 @@
     <col width="56" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>MIX SHOP DIGITAL</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
+    <row r="1" ht="38" customHeight="1">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>AJUSTES</t>
         </is>
       </c>
+      <c r="D1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Cargalos una sola vez</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="4" customHeight="1">
-      <c r="B3" s="5" t="n"/>
+    <row r="3" ht="5" customHeight="1">
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="10" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>← VOLVER</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Completá solamente las celdas amarillas. Estos datos aparecen en tus presupuestos y recibos.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="38" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>1. TU NEGOCIO</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="B7" s="83" t="inlineStr">
+      <c r="B7" s="89" t="inlineStr">
         <is>
           <t>Nombre del negocio</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>Mi negocio</t>
         </is>
       </c>
-      <c r="D7" s="84" t="inlineStr">
+      <c r="D7" s="90" t="inlineStr">
         <is>
           <t>Aparece arriba en el presupuesto y el recibo.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="B8" s="83" t="inlineStr">
+      <c r="B8" s="89" t="inlineStr">
         <is>
           <t>RUC o C.I.</t>
         </is>
       </c>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="84" t="inlineStr">
+      <c r="C8" s="20" t="n"/>
+      <c r="D8" s="90" t="inlineStr">
         <is>
           <t>Opcional.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="B9" s="83" t="inlineStr">
+      <c r="B9" s="89" t="inlineStr">
         <is>
           <t>Teléfono</t>
         </is>
       </c>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="84" t="inlineStr">
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="90" t="inlineStr">
         <is>
           <t>Opcional.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="B10" s="83" t="inlineStr">
+      <c r="B10" s="89" t="inlineStr">
         <is>
           <t>Dirección o ciudad</t>
         </is>
       </c>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="84" t="inlineStr">
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="90" t="inlineStr">
         <is>
           <t>Opcional.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="B11" s="83" t="inlineStr">
+      <c r="B11" s="89" t="inlineStr">
         <is>
           <t>Moneda</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>Gs.</t>
         </is>
       </c>
-      <c r="D11" s="84" t="inlineStr">
+      <c r="D11" s="90" t="inlineStr">
         <is>
           <t>Símbolo que se muestra en las hojas.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="B12" s="83" t="inlineStr">
+      <c r="B12" s="89" t="inlineStr">
         <is>
           <t>Año a controlar</t>
         </is>
       </c>
-      <c r="C12" s="85" t="n">
+      <c r="C12" s="91" t="n">
         <v>2026</v>
       </c>
-      <c r="D12" s="84" t="inlineStr">
+      <c r="D12" s="90" t="inlineStr">
         <is>
           <t>El PANEL muestra los 12 meses de este año.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="B13" s="83" t="inlineStr">
+      <c r="B13" s="89" t="inlineStr">
         <is>
           <t>Validez del presupuesto (días)</t>
         </is>
       </c>
-      <c r="C13" s="85" t="n">
+      <c r="C13" s="91" t="n">
         <v>15</v>
       </c>
-      <c r="D13" s="84" t="inlineStr">
+      <c r="D13" s="90" t="inlineStr">
         <is>
           <t>Se usa para calcular la fecha «Válido hasta».</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="83" t="inlineStr">
+      <c r="B14" s="89" t="inlineStr">
         <is>
           <t>Decimales (automático)</t>
         </is>
       </c>
-      <c r="C14" s="86">
+      <c r="C14" s="92">
         <f>IF(Moneda="Gs.",0,2)</f>
         <v/>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>El guaraní no usa decimales; otras monedas usan 2.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="41" t="inlineStr">
+      <c r="B16" s="47" t="inlineStr">
         <is>
           <t>2. TASAS DE IVA (fijadas por ley)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="83" t="inlineStr">
+      <c r="B17" s="89" t="inlineStr">
         <is>
           <t>Tasa general</t>
         </is>
       </c>
-      <c r="C17" s="87" t="n">
+      <c r="C17" s="93" t="n">
         <v>0.1</v>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>10 % — Ley 125/91, modificada por la Ley 6380/2019.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="83" t="inlineStr">
+      <c r="B18" s="89" t="inlineStr">
         <is>
           <t>Tasa reducida</t>
         </is>
       </c>
-      <c r="C18" s="87" t="n">
+      <c r="C18" s="93" t="n">
         <v>0.05</v>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>5 % — productos y servicios con tasa reducida.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="8" customHeight="1">
-      <c r="B21" s="34" t="n"/>
+      <c r="B21" s="40" t="n"/>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="B22" s="35" t="inlineStr">
+      <c r="B22" s="41" t="inlineStr">
         <is>
           <t>MIX SHOP DIGITAL  ·  Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="B23" s="36" t="inlineStr">
+      <c r="B23" s="42" t="inlineStr">
         <is>
           <t>Versión gratuita  ·  Para gestionar todo tu negocio en un solo lugar, conocé Mi Negocio PY  →  mixshopdigital.com.py</t>
         </is>
@@ -4099,8 +4346,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8CA3"/>
-  <mergeCells count="9">
-    <mergeCell ref="B3:D3"/>
+  <mergeCells count="8">
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="B23:D23"/>
@@ -4138,6 +4384,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -4161,204 +4408,211 @@
     <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>MIX SHOP DIGITAL</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
+    <row r="1" ht="38" customHeight="1">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>AYUDA</t>
         </is>
       </c>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Se aprende en 2 minutos</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="4" customHeight="1">
-      <c r="B3" s="5" t="n"/>
+    <row r="3" ht="5" customHeight="1">
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="9" t="n"/>
+      <c r="F3" s="9" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>← VOLVER</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Leé esta hoja una vez. Después ya no la vas a necesitar.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="38" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>¿PARA QUÉ SIRVE?</t>
         </is>
       </c>
     </row>
     <row r="7" ht="33" customHeight="1">
-      <c r="B7" s="88" t="inlineStr">
+      <c r="B7" s="94" t="inlineStr">
         <is>
           <t>Para armar un presupuesto prolijo, darle un recibo a tu cliente y saber cuánto tenés enviado, aprobado y cobrado. Sin fórmulas y sin Internet.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="41" t="inlineStr">
+      <c r="B9" s="47" t="inlineStr">
         <is>
           <t>EMPEZÁ EN 4 PASOS</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18.5" customHeight="1">
-      <c r="B10" s="88" t="inlineStr">
+      <c r="B10" s="94" t="inlineStr">
         <is>
           <t>1) En AJUSTES poné el nombre de tu negocio, tus datos y la validez de tus presupuestos.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="33" customHeight="1">
-      <c r="B11" s="88" t="inlineStr">
+      <c r="B11" s="94" t="inlineStr">
         <is>
           <t>2) En PRESUPUESTO completá los datos del cliente y los ítems. El IVA y el total se calculan solos. Después imprimilo o guardalo en PDF (Archivo &gt; Imprimir).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18.5" customHeight="1">
-      <c r="B12" s="88" t="inlineStr">
+      <c r="B12" s="94" t="inlineStr">
         <is>
           <t>3) Anotá el presupuesto en HISTORIAL y cambiá su estado cuando lo aprueben o lo cobren.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="33" customHeight="1">
-      <c r="B13" s="88" t="inlineStr">
+      <c r="B13" s="94" t="inlineStr">
         <is>
           <t>4) Cuando te paguen, completá el RECIBO. Si dejás celdas vacías, usa el cliente y el total del presupuesto.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="41" t="inlineStr">
+      <c r="B15" s="47" t="inlineStr">
         <is>
           <t>COLORES</t>
         </is>
       </c>
     </row>
     <row r="16" ht="33" customHeight="1">
-      <c r="B16" s="88" t="inlineStr">
+      <c r="B16" s="94" t="inlineStr">
         <is>
           <t>Rosado claro: celdas que completás vos.   Gris o blanco: se calcula solo (bloqueado).   Vino: títulos y totales.   Verde: cobrado.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="38" t="inlineStr">
+      <c r="B18" s="44" t="inlineStr">
         <is>
           <t>PREGUNTAS FRECUENTES</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18.5" customHeight="1">
-      <c r="B19" s="88" t="inlineStr">
+      <c r="B19" s="94" t="inlineStr">
         <is>
           <t>• Veo todo en cero: hacé clic en «Habilitar edición» en la barra amarilla de Excel.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="33" customHeight="1">
-      <c r="B20" s="88" t="inlineStr">
+      <c r="B20" s="94" t="inlineStr">
         <is>
           <t>• ¿Cómo hago otro presupuesto? Guardá una copia del archivo y borrá los ítems y datos del cliente (celdas rosadas), o escribí encima.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18.5" customHeight="1">
-      <c r="B21" s="88" t="inlineStr">
+      <c r="B21" s="94" t="inlineStr">
         <is>
           <t>• ¿Puedo cobrar en partes? Sí: en el RECIBO escribí el monto recibido y mirá el saldo pendiente.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="33" customHeight="1">
-      <c r="B22" s="88" t="inlineStr">
+      <c r="B22" s="94" t="inlineStr">
         <is>
           <t>• ¿Los precios llevan IVA? Elegí «Ya incluyen el IVA» o «No incluyen el IVA (se suma)». La planilla muestra el IVA discriminado.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="33" customHeight="1">
-      <c r="B23" s="88" t="inlineStr">
+      <c r="B23" s="94" t="inlineStr">
         <is>
           <t>• ¿Cuántos ítems entran? 12 por presupuesto y 100 presupuestos en el HISTORIAL. Cuando se llene, duplicá el archivo y usá otro por año.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="33" customHeight="1">
-      <c r="B24" s="88" t="inlineStr">
+      <c r="B24" s="94" t="inlineStr">
         <is>
           <t>• Solo se editan las celdas rosadas: el resto está protegido para que no se rompan las fórmulas por accidente.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="38" t="inlineStr">
+      <c r="B26" s="44" t="inlineStr">
         <is>
           <t>SOBRE LA PROTECCIÓN</t>
         </is>
       </c>
     </row>
     <row r="27" ht="47.5" customHeight="1">
-      <c r="B27" s="88" t="inlineStr">
+      <c r="B27" s="94" t="inlineStr">
         <is>
           <t>La protección de Excel evita borrados accidentales, pero no es un sistema de seguridad criptográfico. Es una herramienta orientativa: los comprobantes con validez tributaria se emiten con tu timbrado, según corresponda.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="89" t="inlineStr">
+      <c r="B29" s="95" t="inlineStr">
         <is>
           <t>MIX SHOP DIGITAL Y MI NEGOCIO PY</t>
         </is>
       </c>
     </row>
     <row r="30" ht="33" customHeight="1">
-      <c r="B30" s="88" t="inlineStr">
+      <c r="B30" s="94" t="inlineStr">
         <is>
           <t>Esta planilla es una herramienta gratuita de Mix Shop Digital. Si querés gestionar todo tu negocio en un solo lugar, conocé Mi Negocio PY, el sistema de gestión para pequeños negocios de Paraguay.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="90" t="inlineStr">
+      <c r="B31" s="96" t="inlineStr">
         <is>
           <t>→ mixshopdigital.com.py</t>
         </is>
       </c>
     </row>
     <row r="33" ht="8" customHeight="1">
-      <c r="B33" s="34" t="n"/>
+      <c r="B33" s="40" t="n"/>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="B34" s="35" t="inlineStr">
+      <c r="B34" s="41" t="inlineStr">
         <is>
           <t>MIX SHOP DIGITAL  ·  Herramientas inteligentes que simplifican tu vida.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="B35" s="36" t="inlineStr">
+      <c r="B35" s="42" t="inlineStr">
         <is>
           <t>Versión gratuita  ·  Para gestionar todo tu negocio en un solo lugar, conocé Mi Negocio PY  →  mixshopdigital.com.py</t>
         </is>
@@ -4366,7 +4620,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8CA3"/>
-  <mergeCells count="30">
+  <mergeCells count="29">
     <mergeCell ref="B9:H9"/>
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="B6:H6"/>
@@ -4382,7 +4636,6 @@
     <mergeCell ref="B16:H16"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B3:H3"/>
     <mergeCell ref="B31:H31"/>
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="B18:H18"/>
@@ -4414,5 +4667,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
 </worksheet>
 </file>